--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>27/07/2026 a las 16:13:42</t>
+    <t>27/07/2026 a las 16:16:42</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -63912,7 +63912,7 @@
         <v>0</v>
       </c>
       <c r="X693" s="4" t="s">
-        <v>267</v>
+        <v>1258</v>
       </c>
       <c r="Y693" s="4"/>
       <c r="Z693" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3703">
   <si>
     <t>DELTEC - GUAJIRA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>27/07/2026 a las 16:16:42</t>
+    <t>27/07/2026 a las 16:22:22</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -11016,15 +11016,6 @@
   </si>
   <si>
     <t>12190838-MCA54</t>
-  </si>
-  <si>
-    <t>CL 9 CR 7 - 109 DPL EH6361</t>
-  </si>
-  <si>
-    <t>DAVID PLATA  BETTY E.</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. JOSE OSCAR CORTES RODRIGUEZ 3186331483 REV DEL MD CONEXIONES CONSUMO ESTIMADO Y OSCILACION DE VOLTAJE</t>
   </si>
   <si>
     <t>SEIS DE ABRIL</t>
@@ -11526,7 +11517,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB960"/>
+  <dimension ref="A1:AB959"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -50206,7 +50197,7 @@
         <v>0</v>
       </c>
       <c r="X512" s="4" t="s">
-        <v>267</v>
+        <v>1258</v>
       </c>
       <c r="Y512" s="4"/>
       <c r="Z512" s="4" t="s">
@@ -52658,7 +52649,7 @@
         <v>2</v>
       </c>
       <c r="X544" s="4" t="s">
-        <v>267</v>
+        <v>1258</v>
       </c>
       <c r="Y544" s="4"/>
       <c r="Z544" s="4" t="s">
@@ -64406,7 +64397,7 @@
         <v>1000</v>
       </c>
       <c r="B700" s="4" t="s">
-        <v>33</v>
+        <v>1802</v>
       </c>
       <c r="C700" s="4">
         <v>162582170</v>
@@ -64468,7 +64459,7 @@
         <v>4</v>
       </c>
       <c r="X700" s="4" t="s">
-        <v>46</v>
+        <v>267</v>
       </c>
       <c r="Y700" s="4"/>
       <c r="Z700" s="4" t="s">
@@ -83266,16 +83257,16 @@
         <v>1000</v>
       </c>
       <c r="B950" s="4" t="s">
-        <v>3265</v>
+        <v>33</v>
       </c>
       <c r="C950" s="4">
-        <v>162002564</v>
+        <v>152868356</v>
       </c>
       <c r="D950" s="4" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="E950" s="4">
-        <v>5613347</v>
+        <v>7511633</v>
       </c>
       <c r="F950" s="4" t="s">
         <v>244</v>
@@ -83290,51 +83281,49 @@
         <v>3590</v>
       </c>
       <c r="J950" s="4" t="s">
-        <v>3653</v>
+        <v>3667</v>
       </c>
       <c r="K950" s="4"/>
       <c r="L950" s="4" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="M950" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N950" s="4">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="O950" s="4" t="s">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="P950" s="5"/>
       <c r="Q950" s="4" t="s">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="R950" s="4" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="S950" s="4">
-        <v>130815.22</v>
+        <v>0</v>
       </c>
       <c r="T950" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U950" s="4"/>
       <c r="V950" s="4"/>
       <c r="W950" s="4">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="X950" s="4" t="s">
-        <v>1710</v>
+        <v>46</v>
       </c>
       <c r="Y950" s="4"/>
       <c r="Z950" s="4" t="s">
-        <v>3669</v>
-      </c>
-      <c r="AA950" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>3670</v>
+      </c>
+      <c r="AA950" s="4"/>
       <c r="AB950" s="4" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="951" spans="1:28">
@@ -83345,13 +83334,13 @@
         <v>33</v>
       </c>
       <c r="C951" s="4">
-        <v>152868356</v>
+        <v>150505450</v>
       </c>
       <c r="D951" s="4" t="s">
         <v>143</v>
       </c>
       <c r="E951" s="4">
-        <v>7511633</v>
+        <v>5611370</v>
       </c>
       <c r="F951" s="4" t="s">
         <v>244</v>
@@ -83366,24 +83355,24 @@
         <v>3590</v>
       </c>
       <c r="J951" s="4" t="s">
-        <v>3670</v>
+        <v>3667</v>
       </c>
       <c r="K951" s="4"/>
       <c r="L951" s="4" t="s">
-        <v>281</v>
+        <v>1136</v>
       </c>
       <c r="M951" s="4" t="s">
         <v>239</v>
       </c>
       <c r="N951" s="4">
-        <v>5</v>
+        <v>90001</v>
       </c>
       <c r="O951" s="4" t="s">
         <v>3671</v>
       </c>
       <c r="P951" s="5"/>
       <c r="Q951" s="4" t="s">
-        <v>3672</v>
+        <v>3669</v>
       </c>
       <c r="R951" s="4" t="s">
         <v>107</v>
@@ -83394,10 +83383,14 @@
       <c r="T951" s="4">
         <v>0</v>
       </c>
-      <c r="U951" s="4"/>
-      <c r="V951" s="4"/>
+      <c r="U951" s="4" t="s">
+        <v>3672</v>
+      </c>
+      <c r="V951" s="4" t="s">
+        <v>187</v>
+      </c>
       <c r="W951" s="4">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="X951" s="4" t="s">
         <v>46</v>
@@ -83419,13 +83412,13 @@
         <v>33</v>
       </c>
       <c r="C952" s="4">
-        <v>150505450</v>
+        <v>159754325</v>
       </c>
       <c r="D952" s="4" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="E952" s="4">
-        <v>5611370</v>
+        <v>5609821</v>
       </c>
       <c r="F952" s="4" t="s">
         <v>244</v>
@@ -83440,24 +83433,24 @@
         <v>3590</v>
       </c>
       <c r="J952" s="4" t="s">
-        <v>3670</v>
+        <v>3674</v>
       </c>
       <c r="K952" s="4"/>
       <c r="L952" s="4" t="s">
-        <v>1136</v>
+        <v>318</v>
       </c>
       <c r="M952" s="4" t="s">
-        <v>239</v>
+        <v>588</v>
       </c>
       <c r="N952" s="4">
-        <v>90001</v>
+        <v>18</v>
       </c>
       <c r="O952" s="4" t="s">
-        <v>3674</v>
+        <v>3675</v>
       </c>
       <c r="P952" s="5"/>
       <c r="Q952" s="4" t="s">
-        <v>3672</v>
+        <v>3676</v>
       </c>
       <c r="R952" s="4" t="s">
         <v>107</v>
@@ -83469,20 +83462,20 @@
         <v>0</v>
       </c>
       <c r="U952" s="4" t="s">
-        <v>3675</v>
+        <v>3677</v>
       </c>
       <c r="V952" s="4" t="s">
-        <v>187</v>
+        <v>1092</v>
       </c>
       <c r="W952" s="4">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="X952" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y952" s="4"/>
       <c r="Z952" s="4" t="s">
-        <v>3676</v>
+        <v>3678</v>
       </c>
       <c r="AA952" s="4"/>
       <c r="AB952" s="4" t="s">
@@ -83497,13 +83490,13 @@
         <v>33</v>
       </c>
       <c r="C953" s="4">
-        <v>159754325</v>
+        <v>162834410</v>
       </c>
       <c r="D953" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E953" s="4">
-        <v>5609821</v>
+        <v>6941336</v>
       </c>
       <c r="F953" s="4" t="s">
         <v>244</v>
@@ -83518,27 +83511,27 @@
         <v>3590</v>
       </c>
       <c r="J953" s="4" t="s">
-        <v>3677</v>
+        <v>3674</v>
       </c>
       <c r="K953" s="4"/>
       <c r="L953" s="4" t="s">
-        <v>318</v>
+        <v>584</v>
       </c>
       <c r="M953" s="4" t="s">
-        <v>588</v>
+        <v>292</v>
       </c>
       <c r="N953" s="4">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="O953" s="4" t="s">
-        <v>3678</v>
+        <v>3679</v>
       </c>
       <c r="P953" s="5"/>
       <c r="Q953" s="4" t="s">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="R953" s="4" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="S953" s="4">
         <v>0</v>
@@ -83547,22 +83540,24 @@
         <v>0</v>
       </c>
       <c r="U953" s="4" t="s">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="V953" s="4" t="s">
-        <v>1092</v>
+        <v>192</v>
       </c>
       <c r="W953" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X953" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y953" s="4"/>
       <c r="Z953" s="4" t="s">
-        <v>3681</v>
-      </c>
-      <c r="AA953" s="4"/>
+        <v>3682</v>
+      </c>
+      <c r="AA953" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB953" s="4" t="s">
         <v>49</v>
       </c>
@@ -83575,7 +83570,7 @@
         <v>33</v>
       </c>
       <c r="C954" s="4">
-        <v>162834410</v>
+        <v>162834476</v>
       </c>
       <c r="D954" s="4" t="s">
         <v>58</v>
@@ -83596,7 +83591,7 @@
         <v>3590</v>
       </c>
       <c r="J954" s="4" t="s">
-        <v>3677</v>
+        <v>3674</v>
       </c>
       <c r="K954" s="4"/>
       <c r="L954" s="4" t="s">
@@ -83609,11 +83604,11 @@
         <v>53</v>
       </c>
       <c r="O954" s="4" t="s">
-        <v>3682</v>
+        <v>3679</v>
       </c>
       <c r="P954" s="5"/>
       <c r="Q954" s="4" t="s">
-        <v>3683</v>
+        <v>3680</v>
       </c>
       <c r="R954" s="4" t="s">
         <v>56</v>
@@ -83625,7 +83620,7 @@
         <v>0</v>
       </c>
       <c r="U954" s="4" t="s">
-        <v>3684</v>
+        <v>3681</v>
       </c>
       <c r="V954" s="4" t="s">
         <v>192</v>
@@ -83638,7 +83633,7 @@
       </c>
       <c r="Y954" s="4"/>
       <c r="Z954" s="4" t="s">
-        <v>3685</v>
+        <v>3683</v>
       </c>
       <c r="AA954" s="4" t="s">
         <v>48</v>
@@ -83652,16 +83647,16 @@
         <v>1000</v>
       </c>
       <c r="B955" s="4" t="s">
-        <v>33</v>
+        <v>3265</v>
       </c>
       <c r="C955" s="4">
-        <v>162834476</v>
+        <v>161827649</v>
       </c>
       <c r="D955" s="4" t="s">
         <v>58</v>
       </c>
       <c r="E955" s="4">
-        <v>6941336</v>
+        <v>6268676</v>
       </c>
       <c r="F955" s="4" t="s">
         <v>244</v>
@@ -83676,27 +83671,25 @@
         <v>3590</v>
       </c>
       <c r="J955" s="4" t="s">
-        <v>3677</v>
+        <v>3674</v>
       </c>
       <c r="K955" s="4"/>
       <c r="L955" s="4" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="M955" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="N955" s="4">
-        <v>53</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="N955" s="4"/>
       <c r="O955" s="4" t="s">
-        <v>3682</v>
+        <v>3684</v>
       </c>
       <c r="P955" s="5"/>
       <c r="Q955" s="4" t="s">
-        <v>3683</v>
+        <v>3685</v>
       </c>
       <c r="R955" s="4" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="S955" s="4">
         <v>0</v>
@@ -83704,25 +83697,19 @@
       <c r="T955" s="4">
         <v>0</v>
       </c>
-      <c r="U955" s="4" t="s">
-        <v>3684</v>
-      </c>
-      <c r="V955" s="4" t="s">
-        <v>192</v>
-      </c>
+      <c r="U955" s="4"/>
+      <c r="V955" s="4"/>
       <c r="W955" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X955" s="4" t="s">
-        <v>46</v>
+        <v>267</v>
       </c>
       <c r="Y955" s="4"/>
       <c r="Z955" s="4" t="s">
         <v>3686</v>
       </c>
-      <c r="AA955" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="AA955" s="4"/>
       <c r="AB955" s="4" t="s">
         <v>49</v>
       </c>
@@ -83732,16 +83719,16 @@
         <v>1000</v>
       </c>
       <c r="B956" s="4" t="s">
-        <v>3265</v>
+        <v>33</v>
       </c>
       <c r="C956" s="4">
-        <v>161827649</v>
+        <v>150816514</v>
       </c>
       <c r="D956" s="4" t="s">
-        <v>58</v>
+        <v>251</v>
       </c>
       <c r="E956" s="4">
-        <v>6268676</v>
+        <v>8186939</v>
       </c>
       <c r="F956" s="4" t="s">
         <v>244</v>
@@ -83756,25 +83743,27 @@
         <v>3590</v>
       </c>
       <c r="J956" s="4" t="s">
-        <v>3677</v>
+        <v>3674</v>
       </c>
       <c r="K956" s="4"/>
       <c r="L956" s="4" t="s">
-        <v>588</v>
+        <v>724</v>
       </c>
       <c r="M956" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="N956" s="4"/>
+        <v>3687</v>
+      </c>
+      <c r="N956" s="4">
+        <v>70</v>
+      </c>
       <c r="O956" s="4" t="s">
-        <v>3687</v>
+        <v>3688</v>
       </c>
       <c r="P956" s="5"/>
       <c r="Q956" s="4" t="s">
-        <v>3688</v>
+        <v>3689</v>
       </c>
       <c r="R956" s="4" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="S956" s="4">
         <v>0</v>
@@ -83785,14 +83774,14 @@
       <c r="U956" s="4"/>
       <c r="V956" s="4"/>
       <c r="W956" s="4">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="X956" s="4" t="s">
-        <v>267</v>
+        <v>46</v>
       </c>
       <c r="Y956" s="4"/>
       <c r="Z956" s="4" t="s">
-        <v>3689</v>
+        <v>3690</v>
       </c>
       <c r="AA956" s="4"/>
       <c r="AB956" s="4" t="s">
@@ -83807,13 +83796,13 @@
         <v>33</v>
       </c>
       <c r="C957" s="4">
-        <v>150816514</v>
+        <v>135317231</v>
       </c>
       <c r="D957" s="4" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E957" s="4">
-        <v>8186939</v>
+        <v>8310140</v>
       </c>
       <c r="F957" s="4" t="s">
         <v>244</v>
@@ -83825,30 +83814,24 @@
         <v>3589</v>
       </c>
       <c r="I957" s="4" t="s">
-        <v>3590</v>
+        <v>3691</v>
       </c>
       <c r="J957" s="4" t="s">
-        <v>3677</v>
+        <v>3691</v>
       </c>
       <c r="K957" s="4"/>
-      <c r="L957" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="M957" s="4" t="s">
-        <v>3690</v>
-      </c>
-      <c r="N957" s="4">
-        <v>70</v>
-      </c>
+      <c r="L957" s="4"/>
+      <c r="M957" s="4"/>
+      <c r="N957" s="4"/>
       <c r="O957" s="4" t="s">
-        <v>3691</v>
+        <v>3692</v>
       </c>
       <c r="P957" s="5"/>
       <c r="Q957" s="4" t="s">
-        <v>3692</v>
+        <v>3693</v>
       </c>
       <c r="R957" s="4" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="S957" s="4">
         <v>0</v>
@@ -83859,18 +83842,18 @@
       <c r="U957" s="4"/>
       <c r="V957" s="4"/>
       <c r="W957" s="4">
-        <v>159</v>
+        <v>362</v>
       </c>
       <c r="X957" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y957" s="4"/>
       <c r="Z957" s="4" t="s">
-        <v>3693</v>
+        <v>3694</v>
       </c>
       <c r="AA957" s="4"/>
       <c r="AB957" s="4" t="s">
-        <v>49</v>
+        <v>250</v>
       </c>
     </row>
     <row r="958" spans="1:28">
@@ -83881,13 +83864,13 @@
         <v>33</v>
       </c>
       <c r="C958" s="4">
-        <v>135317231</v>
+        <v>161590131</v>
       </c>
       <c r="D958" s="4" t="s">
-        <v>243</v>
+        <v>2827</v>
       </c>
       <c r="E958" s="4">
-        <v>8310140</v>
+        <v>7606222</v>
       </c>
       <c r="F958" s="4" t="s">
         <v>244</v>
@@ -83899,10 +83882,10 @@
         <v>3589</v>
       </c>
       <c r="I958" s="4" t="s">
-        <v>3694</v>
+        <v>3691</v>
       </c>
       <c r="J958" s="4" t="s">
-        <v>3694</v>
+        <v>3691</v>
       </c>
       <c r="K958" s="4"/>
       <c r="L958" s="4"/>
@@ -83916,29 +83899,35 @@
         <v>3696</v>
       </c>
       <c r="R958" s="4" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="S958" s="4">
-        <v>0</v>
+        <v>142267307.52</v>
       </c>
       <c r="T958" s="4">
-        <v>0</v>
-      </c>
-      <c r="U958" s="4"/>
-      <c r="V958" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="U958" s="4" t="s">
+        <v>3697</v>
+      </c>
+      <c r="V958" s="4" t="s">
+        <v>220</v>
+      </c>
       <c r="W958" s="4">
-        <v>362</v>
+        <v>14</v>
       </c>
       <c r="X958" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y958" s="4"/>
       <c r="Z958" s="4" t="s">
-        <v>3697</v>
-      </c>
-      <c r="AA958" s="4"/>
+        <v>3698</v>
+      </c>
+      <c r="AA958" s="4" t="s">
+        <v>471</v>
+      </c>
       <c r="AB958" s="4" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
     </row>
     <row r="959" spans="1:28">
@@ -83946,16 +83935,16 @@
         <v>1000</v>
       </c>
       <c r="B959" s="4" t="s">
-        <v>33</v>
+        <v>3265</v>
       </c>
       <c r="C959" s="4">
-        <v>161590131</v>
+        <v>161215256</v>
       </c>
       <c r="D959" s="4" t="s">
-        <v>2827</v>
+        <v>58</v>
       </c>
       <c r="E959" s="4">
-        <v>7606222</v>
+        <v>5614888</v>
       </c>
       <c r="F959" s="4" t="s">
         <v>244</v>
@@ -83967,127 +83956,53 @@
         <v>3589</v>
       </c>
       <c r="I959" s="4" t="s">
-        <v>3694</v>
+        <v>3590</v>
       </c>
       <c r="J959" s="4" t="s">
-        <v>3694</v>
+        <v>3699</v>
       </c>
       <c r="K959" s="4"/>
-      <c r="L959" s="4"/>
-      <c r="M959" s="4"/>
-      <c r="N959" s="4"/>
+      <c r="L959" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M959" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="N959" s="4">
+        <v>12</v>
+      </c>
       <c r="O959" s="4" t="s">
-        <v>3698</v>
+        <v>3700</v>
       </c>
       <c r="P959" s="5"/>
       <c r="Q959" s="4" t="s">
-        <v>3699</v>
+        <v>3701</v>
       </c>
       <c r="R959" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="S959" s="4">
-        <v>142267307.52</v>
+        <v>77914.81</v>
       </c>
       <c r="T959" s="4">
-        <v>17</v>
-      </c>
-      <c r="U959" s="4" t="s">
-        <v>3700</v>
-      </c>
-      <c r="V959" s="4" t="s">
-        <v>220</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U959" s="4"/>
+      <c r="V959" s="4"/>
       <c r="W959" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="X959" s="4" t="s">
-        <v>46</v>
+        <v>267</v>
       </c>
       <c r="Y959" s="4"/>
       <c r="Z959" s="4" t="s">
-        <v>3701</v>
+        <v>3702</v>
       </c>
       <c r="AA959" s="4" t="s">
-        <v>471</v>
+        <v>48</v>
       </c>
       <c r="AB959" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="960" spans="1:28">
-      <c r="A960" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B960" s="4" t="s">
-        <v>3265</v>
-      </c>
-      <c r="C960" s="4">
-        <v>161215256</v>
-      </c>
-      <c r="D960" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E960" s="4">
-        <v>5614888</v>
-      </c>
-      <c r="F960" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="G960" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H960" s="4" t="s">
-        <v>3589</v>
-      </c>
-      <c r="I960" s="4" t="s">
-        <v>3590</v>
-      </c>
-      <c r="J960" s="4" t="s">
-        <v>3702</v>
-      </c>
-      <c r="K960" s="4"/>
-      <c r="L960" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="M960" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="N960" s="4">
-        <v>12</v>
-      </c>
-      <c r="O960" s="4" t="s">
-        <v>3703</v>
-      </c>
-      <c r="P960" s="5"/>
-      <c r="Q960" s="4" t="s">
-        <v>3704</v>
-      </c>
-      <c r="R960" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="S960" s="4">
-        <v>77914.81</v>
-      </c>
-      <c r="T960" s="4">
-        <v>1</v>
-      </c>
-      <c r="U960" s="4"/>
-      <c r="V960" s="4"/>
-      <c r="W960" s="4">
-        <v>20</v>
-      </c>
-      <c r="X960" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="Y960" s="4"/>
-      <c r="Z960" s="4" t="s">
-        <v>3705</v>
-      </c>
-      <c r="AA960" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB960" s="4" t="s">
         <v>49</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>30/07/2026 a las 07:15:33</t>
+    <t>30/07/2026 a las 07:31:55</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -8738,6 +8738,9 @@
     <t>REDONDO OJEDA  DAMELIS JOSEFINA</t>
   </si>
   <si>
+    <t>Comprometida</t>
+  </si>
+  <si>
     <t>Revision Suministromedidor MD Camp.Dirigidas SUSPENSION EN TENDIDO. 060-02-Acciones Focalizadas-GUA Medidor con puentes en bornera</t>
   </si>
   <si>
@@ -9170,9 +9173,6 @@
     <t>VERGARA  JESUS</t>
   </si>
   <si>
-    <t>Comprometida</t>
-  </si>
-  <si>
     <t>Revision Suministromedidor MD Analisis Macro SUSPENSION EN TENDIDO. 060-06-RevisionNormalizacion Denuncias-GUA acometida intervenida</t>
   </si>
   <si>
@@ -9224,6 +9224,9 @@
     <t>ALVARADO  ARISTIDES</t>
   </si>
   <si>
+    <t>En Asignacion</t>
+  </si>
+  <si>
     <t>Revision Suministromedidor MD Analisis Macro 110-01-RevisionNormalizacion PCI-GUA  predio ocupado con energia medidor manipulado puente verificar acometida posible intervenida bajos consumos casa grande reubicar medidor limite de propiedad  medidor manipulado puente verificar acometida posible</t>
   </si>
   <si>
@@ -10569,9 +10572,6 @@
   </si>
   <si>
     <t>12227992-MCA54</t>
-  </si>
-  <si>
-    <t>En Asignacion</t>
   </si>
   <si>
     <t>Reubicacion mddor MD PQR SUSPENSION EN TENDIDO. Sra  Luz Urbina  Prop.  Tel. 3016231101 CC 40917441 Motivo de la llamda Solicita reubicacion medidor, informa que el medidor es primera vez que se le instala y le intalaron en el poste, solicita que se le reubique en el predio, se le informa co</t>
@@ -69537,11 +69537,11 @@
         <v>1</v>
       </c>
       <c r="X762" s="4" t="s">
-        <v>515</v>
+        <v>2907</v>
       </c>
       <c r="Y762" s="4"/>
       <c r="Z762" s="4" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="AA762" s="4" t="s">
         <v>48</v>
@@ -69583,7 +69583,7 @@
       </c>
       <c r="K763" s="4"/>
       <c r="L763" s="4" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="M763" s="4" t="s">
         <v>1003</v>
@@ -69592,11 +69592,11 @@
         <v>15</v>
       </c>
       <c r="O763" s="4" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="P763" s="5"/>
       <c r="Q763" s="4" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="R763" s="4" t="s">
         <v>56</v>
@@ -69617,7 +69617,7 @@
       </c>
       <c r="Y763" s="4"/>
       <c r="Z763" s="4" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="AA763" s="4" t="s">
         <v>48</v>
@@ -69668,11 +69668,11 @@
         <v>49</v>
       </c>
       <c r="O764" s="4" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="P764" s="5"/>
       <c r="Q764" s="4" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="R764" s="4" t="s">
         <v>56</v>
@@ -69684,7 +69684,7 @@
         <v>4</v>
       </c>
       <c r="U764" s="4" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="V764" s="4" t="s">
         <v>317</v>
@@ -69697,7 +69697,7 @@
       </c>
       <c r="Y764" s="4"/>
       <c r="Z764" s="4" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="AA764" s="4" t="s">
         <v>48</v>
@@ -69735,7 +69735,7 @@
         <v>1690</v>
       </c>
       <c r="J765" s="4" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="K765" s="4"/>
       <c r="L765" s="4" t="s">
@@ -69748,11 +69748,11 @@
         <v>55</v>
       </c>
       <c r="O765" s="4" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="P765" s="5"/>
       <c r="Q765" s="4" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="R765" s="4" t="s">
         <v>56</v>
@@ -69764,7 +69764,7 @@
         <v>28</v>
       </c>
       <c r="U765" s="4" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="V765" s="4" t="s">
         <v>825</v>
@@ -69777,7 +69777,7 @@
       </c>
       <c r="Y765" s="4"/>
       <c r="Z765" s="4" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="AA765" s="4" t="s">
         <v>77</v>
@@ -69815,11 +69815,11 @@
         <v>1690</v>
       </c>
       <c r="J766" s="4" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="K766" s="4"/>
       <c r="L766" s="4" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="M766" s="4" t="s">
         <v>300</v>
@@ -69828,11 +69828,11 @@
         <v>79</v>
       </c>
       <c r="O766" s="4" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="P766" s="5"/>
       <c r="Q766" s="4" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="R766" s="4" t="s">
         <v>43</v>
@@ -69853,7 +69853,7 @@
       </c>
       <c r="Y766" s="4"/>
       <c r="Z766" s="4" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="AA766" s="4"/>
       <c r="AB766" s="4" t="s">
@@ -69889,7 +69889,7 @@
         <v>1690</v>
       </c>
       <c r="J767" s="4" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="K767" s="4"/>
       <c r="L767" s="4" t="s">
@@ -69902,11 +69902,11 @@
         <v>26</v>
       </c>
       <c r="O767" s="4" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="P767" s="5"/>
       <c r="Q767" s="4" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="R767" s="4" t="s">
         <v>63</v>
@@ -69918,7 +69918,7 @@
         <v>0</v>
       </c>
       <c r="U767" s="4" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="V767" s="4" t="s">
         <v>614</v>
@@ -69931,7 +69931,7 @@
       </c>
       <c r="Y767" s="4"/>
       <c r="Z767" s="4" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="AA767" s="4" t="s">
         <v>48</v>
@@ -69969,24 +69969,24 @@
         <v>1690</v>
       </c>
       <c r="J768" s="4" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="K768" s="4"/>
       <c r="L768" s="4" t="s">
         <v>300</v>
       </c>
       <c r="M768" s="4" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="N768" s="4">
         <v>56</v>
       </c>
       <c r="O768" s="4" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="P768" s="5"/>
       <c r="Q768" s="4" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="R768" s="4" t="s">
         <v>63</v>
@@ -70007,7 +70007,7 @@
       </c>
       <c r="Y768" s="4"/>
       <c r="Z768" s="4" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="AA768" s="4" t="s">
         <v>48</v>
@@ -70045,11 +70045,11 @@
         <v>1690</v>
       </c>
       <c r="J769" s="4" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="K769" s="4"/>
       <c r="L769" s="4" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="M769" s="4" t="s">
         <v>1270</v>
@@ -70058,11 +70058,11 @@
         <v>96</v>
       </c>
       <c r="O769" s="4" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="P769" s="5"/>
       <c r="Q769" s="4" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="R769" s="4" t="s">
         <v>56</v>
@@ -70074,7 +70074,7 @@
         <v>1</v>
       </c>
       <c r="U769" s="4" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="V769" s="4" t="s">
         <v>363</v>
@@ -70122,21 +70122,21 @@
         <v>1690</v>
       </c>
       <c r="I770" s="4" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="J770" s="4" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="K770" s="4"/>
       <c r="L770" s="4"/>
       <c r="M770" s="4"/>
       <c r="N770" s="4"/>
       <c r="O770" s="4" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="P770" s="5"/>
       <c r="Q770" s="4" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="R770" s="4" t="s">
         <v>56</v>
@@ -70157,7 +70157,7 @@
       </c>
       <c r="Y770" s="4"/>
       <c r="Z770" s="4" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="AA770" s="4" t="s">
         <v>310</v>
@@ -70192,21 +70192,21 @@
         <v>1690</v>
       </c>
       <c r="I771" s="4" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="J771" s="4" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="K771" s="4"/>
       <c r="L771" s="4"/>
       <c r="M771" s="4"/>
       <c r="N771" s="4"/>
       <c r="O771" s="4" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="P771" s="5"/>
       <c r="Q771" s="4" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="R771" s="4" t="s">
         <v>63</v>
@@ -70265,7 +70265,7 @@
         <v>1690</v>
       </c>
       <c r="J772" s="4" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="K772" s="4"/>
       <c r="L772" s="4" t="s">
@@ -70278,11 +70278,11 @@
         <v>1541</v>
       </c>
       <c r="O772" s="4" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="P772" s="5"/>
       <c r="Q772" s="4" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="R772" s="4" t="s">
         <v>43</v>
@@ -70303,7 +70303,7 @@
       </c>
       <c r="Y772" s="4"/>
       <c r="Z772" s="4" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="AA772" s="4" t="s">
         <v>77</v>
@@ -70341,7 +70341,7 @@
         <v>1690</v>
       </c>
       <c r="J773" s="4" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="K773" s="4"/>
       <c r="L773" s="4" t="s">
@@ -70354,11 +70354,11 @@
         <v>16</v>
       </c>
       <c r="O773" s="4" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="P773" s="5"/>
       <c r="Q773" s="4" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="R773" s="4" t="s">
         <v>43</v>
@@ -70370,7 +70370,7 @@
         <v>0</v>
       </c>
       <c r="U773" s="4" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="V773" s="4" t="s">
         <v>125</v>
@@ -70383,7 +70383,7 @@
       </c>
       <c r="Y773" s="4"/>
       <c r="Z773" s="4" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="AA773" s="4" t="s">
         <v>65</v>
@@ -70418,21 +70418,21 @@
         <v>1690</v>
       </c>
       <c r="I774" s="4" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="J774" s="4" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="K774" s="4"/>
       <c r="L774" s="4"/>
       <c r="M774" s="4"/>
       <c r="N774" s="4"/>
       <c r="O774" s="4" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="P774" s="5"/>
       <c r="Q774" s="4" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="R774" s="4" t="s">
         <v>63</v>
@@ -70444,7 +70444,7 @@
         <v>64</v>
       </c>
       <c r="U774" s="4" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="V774" s="4" t="s">
         <v>335</v>
@@ -70490,10 +70490,10 @@
         <v>1690</v>
       </c>
       <c r="I775" s="4" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="J775" s="4" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="K775" s="4"/>
       <c r="L775" s="4" t="s">
@@ -70506,11 +70506,11 @@
         <v>47</v>
       </c>
       <c r="O775" s="4" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="P775" s="5"/>
       <c r="Q775" s="4" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="R775" s="4" t="s">
         <v>63</v>
@@ -70531,7 +70531,7 @@
       </c>
       <c r="Y775" s="4"/>
       <c r="Z775" s="4" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="AA775" s="4"/>
       <c r="AB775" s="4" t="s">
@@ -70571,7 +70571,7 @@
       </c>
       <c r="K776" s="4"/>
       <c r="L776" s="4" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="M776" s="4" t="s">
         <v>1197</v>
@@ -70580,11 +70580,11 @@
         <v>23</v>
       </c>
       <c r="O776" s="4" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="P776" s="5"/>
       <c r="Q776" s="4" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="R776" s="4" t="s">
         <v>56</v>
@@ -70605,7 +70605,7 @@
       </c>
       <c r="Y776" s="4"/>
       <c r="Z776" s="4" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="AA776" s="4" t="s">
         <v>488</v>
@@ -70647,20 +70647,20 @@
       </c>
       <c r="K777" s="4"/>
       <c r="L777" s="4" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="M777" s="4" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="N777" s="4">
         <v>30</v>
       </c>
       <c r="O777" s="4" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="P777" s="5"/>
       <c r="Q777" s="4" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="R777" s="4" t="s">
         <v>63</v>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="Y777" s="4"/>
       <c r="Z777" s="4" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="AA777" s="4"/>
       <c r="AB777" s="4" t="s">
@@ -70717,7 +70717,7 @@
         <v>1690</v>
       </c>
       <c r="J778" s="4" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="K778" s="4"/>
       <c r="L778" s="4" t="s">
@@ -70730,11 +70730,11 @@
         <v>163</v>
       </c>
       <c r="O778" s="4" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="P778" s="5"/>
       <c r="Q778" s="4" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="R778" s="4" t="s">
         <v>56</v>
@@ -70746,7 +70746,7 @@
         <v>0</v>
       </c>
       <c r="U778" s="4" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="V778" s="4" t="s">
         <v>203</v>
@@ -70797,7 +70797,7 @@
         <v>1690</v>
       </c>
       <c r="J779" s="4" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="K779" s="4"/>
       <c r="L779" s="4" t="s">
@@ -70810,11 +70810,11 @@
         <v>45</v>
       </c>
       <c r="O779" s="4" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="P779" s="5"/>
       <c r="Q779" s="4" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="R779" s="4" t="s">
         <v>56</v>
@@ -70835,7 +70835,7 @@
       </c>
       <c r="Y779" s="4"/>
       <c r="Z779" s="4" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="AA779" s="4" t="s">
         <v>48</v>
@@ -70873,7 +70873,7 @@
         <v>1690</v>
       </c>
       <c r="J780" s="4" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="K780" s="4"/>
       <c r="L780" s="4" t="s">
@@ -70886,11 +70886,11 @@
         <v>53</v>
       </c>
       <c r="O780" s="4" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="P780" s="5"/>
       <c r="Q780" s="4" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="R780" s="4" t="s">
         <v>63</v>
@@ -70911,7 +70911,7 @@
       </c>
       <c r="Y780" s="4"/>
       <c r="Z780" s="4" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="AA780" s="4" t="s">
         <v>48</v>
@@ -70949,7 +70949,7 @@
         <v>1690</v>
       </c>
       <c r="J781" s="4" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="K781" s="4"/>
       <c r="L781" s="4" t="s">
@@ -70962,11 +70962,11 @@
         <v>24</v>
       </c>
       <c r="O781" s="4" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="P781" s="5"/>
       <c r="Q781" s="4" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="R781" s="4" t="s">
         <v>56</v>
@@ -70987,7 +70987,7 @@
       </c>
       <c r="Y781" s="4"/>
       <c r="Z781" s="4" t="s">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="AA781" s="4" t="s">
         <v>48</v>
@@ -71025,7 +71025,7 @@
         <v>1690</v>
       </c>
       <c r="J782" s="4" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="K782" s="4"/>
       <c r="L782" s="4" t="s">
@@ -71038,11 +71038,11 @@
         <v>92</v>
       </c>
       <c r="O782" s="4" t="s">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="P782" s="5"/>
       <c r="Q782" s="4" t="s">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="R782" s="4" t="s">
         <v>56</v>
@@ -71054,7 +71054,7 @@
         <v>0</v>
       </c>
       <c r="U782" s="4" t="s">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="V782" s="4" t="s">
         <v>317</v>
@@ -71067,7 +71067,7 @@
       </c>
       <c r="Y782" s="4"/>
       <c r="Z782" s="4" t="s">
-        <v>2984</v>
+        <v>2985</v>
       </c>
       <c r="AA782" s="4"/>
       <c r="AB782" s="4" t="s">
@@ -71103,11 +71103,11 @@
         <v>1690</v>
       </c>
       <c r="J783" s="4" t="s">
-        <v>2985</v>
+        <v>2986</v>
       </c>
       <c r="K783" s="4"/>
       <c r="L783" s="4" t="s">
-        <v>2986</v>
+        <v>2987</v>
       </c>
       <c r="M783" s="4" t="s">
         <v>2889</v>
@@ -71116,11 +71116,11 @@
         <v>24</v>
       </c>
       <c r="O783" s="4" t="s">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="P783" s="5"/>
       <c r="Q783" s="4" t="s">
-        <v>2988</v>
+        <v>2989</v>
       </c>
       <c r="R783" s="4" t="s">
         <v>56</v>
@@ -71179,11 +71179,11 @@
         <v>1690</v>
       </c>
       <c r="J784" s="4" t="s">
-        <v>2985</v>
+        <v>2986</v>
       </c>
       <c r="K784" s="4"/>
       <c r="L784" s="4" t="s">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="M784" s="4" t="s">
         <v>1838</v>
@@ -71192,11 +71192,11 @@
         <v>17</v>
       </c>
       <c r="O784" s="4" t="s">
-        <v>2990</v>
+        <v>2991</v>
       </c>
       <c r="P784" s="5"/>
       <c r="Q784" s="4" t="s">
-        <v>2991</v>
+        <v>2992</v>
       </c>
       <c r="R784" s="4" t="s">
         <v>56</v>
@@ -71208,7 +71208,7 @@
         <v>0</v>
       </c>
       <c r="U784" s="4" t="s">
-        <v>2992</v>
+        <v>2993</v>
       </c>
       <c r="V784" s="4" t="s">
         <v>198</v>
@@ -71221,7 +71221,7 @@
       </c>
       <c r="Y784" s="4"/>
       <c r="Z784" s="4" t="s">
-        <v>2993</v>
+        <v>2994</v>
       </c>
       <c r="AA784" s="4" t="s">
         <v>48</v>
@@ -71259,11 +71259,11 @@
         <v>1690</v>
       </c>
       <c r="J785" s="4" t="s">
-        <v>2985</v>
+        <v>2986</v>
       </c>
       <c r="K785" s="4"/>
       <c r="L785" s="4" t="s">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="M785" s="4" t="s">
         <v>1838</v>
@@ -71272,11 +71272,11 @@
         <v>43</v>
       </c>
       <c r="O785" s="4" t="s">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="P785" s="5"/>
       <c r="Q785" s="4" t="s">
-        <v>2995</v>
+        <v>2996</v>
       </c>
       <c r="R785" s="4" t="s">
         <v>56</v>
@@ -71288,7 +71288,7 @@
         <v>0</v>
       </c>
       <c r="U785" s="4" t="s">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="V785" s="4" t="s">
         <v>198</v>
@@ -71301,7 +71301,7 @@
       </c>
       <c r="Y785" s="4"/>
       <c r="Z785" s="4" t="s">
-        <v>2997</v>
+        <v>2998</v>
       </c>
       <c r="AA785" s="4"/>
       <c r="AB785" s="4" t="s">
@@ -71337,11 +71337,11 @@
         <v>1690</v>
       </c>
       <c r="J786" s="4" t="s">
-        <v>2985</v>
+        <v>2986</v>
       </c>
       <c r="K786" s="4"/>
       <c r="L786" s="4" t="s">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="M786" s="4" t="s">
         <v>1838</v>
@@ -71350,11 +71350,11 @@
         <v>5</v>
       </c>
       <c r="O786" s="4" t="s">
-        <v>2998</v>
+        <v>2999</v>
       </c>
       <c r="P786" s="5"/>
       <c r="Q786" s="4" t="s">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="R786" s="4" t="s">
         <v>56</v>
@@ -71375,7 +71375,7 @@
       </c>
       <c r="Y786" s="4"/>
       <c r="Z786" s="4" t="s">
-        <v>2997</v>
+        <v>2998</v>
       </c>
       <c r="AA786" s="4"/>
       <c r="AB786" s="4" t="s">
@@ -71411,7 +71411,7 @@
         <v>1690</v>
       </c>
       <c r="J787" s="4" t="s">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="K787" s="4"/>
       <c r="L787" s="4" t="s">
@@ -71424,11 +71424,11 @@
         <v>54</v>
       </c>
       <c r="O787" s="4" t="s">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="P787" s="5"/>
       <c r="Q787" s="4" t="s">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="R787" s="4" t="s">
         <v>296</v>
@@ -71440,7 +71440,7 @@
         <v>3</v>
       </c>
       <c r="U787" s="4" t="s">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="V787" s="4" t="s">
         <v>317</v>
@@ -71453,7 +71453,7 @@
       </c>
       <c r="Y787" s="4"/>
       <c r="Z787" s="4" t="s">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="AA787" s="4" t="s">
         <v>65</v>
@@ -71502,11 +71502,11 @@
       </c>
       <c r="N788" s="4"/>
       <c r="O788" s="4" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="P788" s="5"/>
       <c r="Q788" s="4" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="R788" s="4" t="s">
         <v>56</v>
@@ -71527,7 +71527,7 @@
       </c>
       <c r="Y788" s="4"/>
       <c r="Z788" s="4" t="s">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="AA788" s="4"/>
       <c r="AB788" s="4" t="s">
@@ -71576,11 +71576,11 @@
         <v>35</v>
       </c>
       <c r="O789" s="4" t="s">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="P789" s="5"/>
       <c r="Q789" s="4" t="s">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="R789" s="4" t="s">
         <v>56</v>
@@ -71592,7 +71592,7 @@
         <v>0</v>
       </c>
       <c r="U789" s="4" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="V789" s="4" t="s">
         <v>125</v>
@@ -71605,7 +71605,7 @@
       </c>
       <c r="Y789" s="4"/>
       <c r="Z789" s="4" t="s">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="AA789" s="4" t="s">
         <v>48</v>
@@ -71656,11 +71656,11 @@
         <v>35</v>
       </c>
       <c r="O790" s="4" t="s">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="P790" s="5"/>
       <c r="Q790" s="4" t="s">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="R790" s="4" t="s">
         <v>56</v>
@@ -71681,7 +71681,7 @@
       </c>
       <c r="Y790" s="4"/>
       <c r="Z790" s="4" t="s">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="AA790" s="4" t="s">
         <v>48</v>
@@ -71732,11 +71732,11 @@
         <v>13</v>
       </c>
       <c r="O791" s="4" t="s">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="P791" s="5"/>
       <c r="Q791" s="4" t="s">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="R791" s="4" t="s">
         <v>56</v>
@@ -71748,7 +71748,7 @@
         <v>0</v>
       </c>
       <c r="U791" s="4" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="V791" s="4" t="s">
         <v>125</v>
@@ -71761,7 +71761,7 @@
       </c>
       <c r="Y791" s="4"/>
       <c r="Z791" s="4" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="AA791" s="4" t="s">
         <v>65</v>
@@ -71812,11 +71812,11 @@
         <v>25</v>
       </c>
       <c r="O792" s="4" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="P792" s="5"/>
       <c r="Q792" s="4" t="s">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="R792" s="4" t="s">
         <v>56</v>
@@ -71828,7 +71828,7 @@
         <v>0</v>
       </c>
       <c r="U792" s="4" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="V792" s="4" t="s">
         <v>125</v>
@@ -71841,7 +71841,7 @@
       </c>
       <c r="Y792" s="4"/>
       <c r="Z792" s="4" t="s">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="AA792" s="4" t="s">
         <v>48</v>
@@ -71892,11 +71892,11 @@
         <v>34</v>
       </c>
       <c r="O793" s="4" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="P793" s="5"/>
       <c r="Q793" s="4" t="s">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="R793" s="4" t="s">
         <v>56</v>
@@ -71908,7 +71908,7 @@
         <v>0</v>
       </c>
       <c r="U793" s="4" t="s">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="V793" s="4" t="s">
         <v>825</v>
@@ -71921,7 +71921,7 @@
       </c>
       <c r="Y793" s="4"/>
       <c r="Z793" s="4" t="s">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="AA793" s="4" t="s">
         <v>48</v>
@@ -71972,11 +71972,11 @@
         <v>34</v>
       </c>
       <c r="O794" s="4" t="s">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="P794" s="5"/>
       <c r="Q794" s="4" t="s">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="R794" s="4" t="s">
         <v>56</v>
@@ -71997,7 +71997,7 @@
       </c>
       <c r="Y794" s="4"/>
       <c r="Z794" s="4" t="s">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="AA794" s="4" t="s">
         <v>48</v>
@@ -72048,11 +72048,11 @@
         <v>76</v>
       </c>
       <c r="O795" s="4" t="s">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="P795" s="5"/>
       <c r="Q795" s="4" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="R795" s="4" t="s">
         <v>56</v>
@@ -72064,7 +72064,7 @@
         <v>1</v>
       </c>
       <c r="U795" s="4" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="V795" s="4" t="s">
         <v>1583</v>
@@ -72077,7 +72077,7 @@
       </c>
       <c r="Y795" s="4"/>
       <c r="Z795" s="4" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="AA795" s="4" t="s">
         <v>65</v>
@@ -72128,11 +72128,11 @@
         <v>90</v>
       </c>
       <c r="O796" s="4" t="s">
-        <v>3033</v>
+        <v>3034</v>
       </c>
       <c r="P796" s="5"/>
       <c r="Q796" s="4" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="R796" s="4" t="s">
         <v>56</v>
@@ -72144,7 +72144,7 @@
         <v>3</v>
       </c>
       <c r="U796" s="4" t="s">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="V796" s="4" t="s">
         <v>125</v>
@@ -72157,7 +72157,7 @@
       </c>
       <c r="Y796" s="4"/>
       <c r="Z796" s="4" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="AA796" s="4" t="s">
         <v>48</v>
@@ -72208,11 +72208,11 @@
         <v>115</v>
       </c>
       <c r="O797" s="4" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="P797" s="5"/>
       <c r="Q797" s="4" t="s">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="R797" s="4" t="s">
         <v>56</v>
@@ -72224,7 +72224,7 @@
         <v>0</v>
       </c>
       <c r="U797" s="4" t="s">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="V797" s="4" t="s">
         <v>317</v>
@@ -72237,7 +72237,7 @@
       </c>
       <c r="Y797" s="4"/>
       <c r="Z797" s="4" t="s">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="AA797" s="4" t="s">
         <v>48</v>
@@ -72288,11 +72288,11 @@
         <v>35</v>
       </c>
       <c r="O798" s="4" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="P798" s="5"/>
       <c r="Q798" s="4" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="R798" s="4" t="s">
         <v>296</v>
@@ -72304,7 +72304,7 @@
         <v>4</v>
       </c>
       <c r="U798" s="4" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="V798" s="4" t="s">
         <v>1583</v>
@@ -72317,7 +72317,7 @@
       </c>
       <c r="Y798" s="4"/>
       <c r="Z798" s="4" t="s">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="AA798" s="4" t="s">
         <v>65</v>
@@ -72368,11 +72368,11 @@
         <v>46</v>
       </c>
       <c r="O799" s="4" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="P799" s="5"/>
       <c r="Q799" s="4" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="R799" s="4" t="s">
         <v>56</v>
@@ -72384,7 +72384,7 @@
         <v>0</v>
       </c>
       <c r="U799" s="4" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="V799" s="4" t="s">
         <v>2086</v>
@@ -72397,7 +72397,7 @@
       </c>
       <c r="Y799" s="4"/>
       <c r="Z799" s="4" t="s">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="AA799" s="4" t="s">
         <v>48</v>
@@ -72448,11 +72448,11 @@
         <v>74</v>
       </c>
       <c r="O800" s="4" t="s">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="P800" s="5"/>
       <c r="Q800" s="4" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="R800" s="4" t="s">
         <v>56</v>
@@ -72469,7 +72469,7 @@
         <v>1</v>
       </c>
       <c r="X800" s="4" t="s">
-        <v>3051</v>
+        <v>515</v>
       </c>
       <c r="Y800" s="4"/>
       <c r="Z800" s="4" t="s">
@@ -72641,7 +72641,7 @@
         <v>1000</v>
       </c>
       <c r="B803" s="4" t="s">
-        <v>33</v>
+        <v>2767</v>
       </c>
       <c r="C803" s="4">
         <v>162927220</v>
@@ -72701,7 +72701,7 @@
         <v>2</v>
       </c>
       <c r="X803" s="4" t="s">
-        <v>46</v>
+        <v>515</v>
       </c>
       <c r="Y803" s="4"/>
       <c r="Z803" s="4" t="s">
@@ -72717,7 +72717,7 @@
         <v>1000</v>
       </c>
       <c r="B804" s="4" t="s">
-        <v>33</v>
+        <v>2767</v>
       </c>
       <c r="C804" s="4">
         <v>162927222</v>
@@ -72775,11 +72775,11 @@
         <v>2</v>
       </c>
       <c r="X804" s="4" t="s">
-        <v>46</v>
+        <v>3069</v>
       </c>
       <c r="Y804" s="4"/>
       <c r="Z804" s="4" t="s">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="AA804" s="4"/>
       <c r="AB804" s="4" t="s">
@@ -72828,11 +72828,11 @@
         <v>85</v>
       </c>
       <c r="O805" s="4" t="s">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="P805" s="5"/>
       <c r="Q805" s="4" t="s">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="R805" s="4" t="s">
         <v>56</v>
@@ -72844,7 +72844,7 @@
         <v>0</v>
       </c>
       <c r="U805" s="4" t="s">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="V805" s="4" t="s">
         <v>825</v>
@@ -72857,7 +72857,7 @@
       </c>
       <c r="Y805" s="4"/>
       <c r="Z805" s="4" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="AA805" s="4" t="s">
         <v>65</v>
@@ -72908,11 +72908,11 @@
         <v>27</v>
       </c>
       <c r="O806" s="4" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="P806" s="5"/>
       <c r="Q806" s="4" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="R806" s="4" t="s">
         <v>56</v>
@@ -72924,7 +72924,7 @@
         <v>0</v>
       </c>
       <c r="U806" s="4" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="V806" s="4" t="s">
         <v>75</v>
@@ -72937,7 +72937,7 @@
       </c>
       <c r="Y806" s="4"/>
       <c r="Z806" s="4" t="s">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="AA806" s="4"/>
       <c r="AB806" s="4" t="s">
@@ -72970,21 +72970,21 @@
         <v>1690</v>
       </c>
       <c r="I807" s="4" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="J807" s="4" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="K807" s="4"/>
       <c r="L807" s="4"/>
       <c r="M807" s="4"/>
       <c r="N807" s="4"/>
       <c r="O807" s="4" t="s">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="P807" s="5"/>
       <c r="Q807" s="4" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="R807" s="4" t="s">
         <v>43</v>
@@ -73005,7 +73005,7 @@
       </c>
       <c r="Y807" s="4"/>
       <c r="Z807" s="4" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="AA807" s="4"/>
       <c r="AB807" s="4" t="s">
@@ -73038,21 +73038,21 @@
         <v>1690</v>
       </c>
       <c r="I808" s="4" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="J808" s="4" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="K808" s="4"/>
       <c r="L808" s="4"/>
       <c r="M808" s="4"/>
       <c r="N808" s="4"/>
       <c r="O808" s="4" t="s">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="P808" s="5"/>
       <c r="Q808" s="4" t="s">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="R808" s="4" t="s">
         <v>56</v>
@@ -73073,7 +73073,7 @@
       </c>
       <c r="Y808" s="4"/>
       <c r="Z808" s="4" t="s">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="AA808" s="4"/>
       <c r="AB808" s="4" t="s">
@@ -73109,7 +73109,7 @@
         <v>1690</v>
       </c>
       <c r="J809" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K809" s="4"/>
       <c r="L809" s="4" t="s">
@@ -73122,11 +73122,11 @@
         <v>45</v>
       </c>
       <c r="O809" s="4" t="s">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="P809" s="5"/>
       <c r="Q809" s="4" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="R809" s="4" t="s">
         <v>63</v>
@@ -73138,7 +73138,7 @@
         <v>0</v>
       </c>
       <c r="U809" s="4" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="V809" s="4" t="s">
         <v>825</v>
@@ -73151,7 +73151,7 @@
       </c>
       <c r="Y809" s="4"/>
       <c r="Z809" s="4" t="s">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="AA809" s="4" t="s">
         <v>65</v>
@@ -73189,24 +73189,24 @@
         <v>1690</v>
       </c>
       <c r="J810" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K810" s="4"/>
       <c r="L810" s="4" t="s">
         <v>1824</v>
       </c>
       <c r="M810" s="4" t="s">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="N810" s="4">
         <v>37</v>
       </c>
       <c r="O810" s="4" t="s">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="P810" s="5"/>
       <c r="Q810" s="4" t="s">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="R810" s="4" t="s">
         <v>63</v>
@@ -73218,7 +73218,7 @@
         <v>58</v>
       </c>
       <c r="U810" s="4" t="s">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="V810" s="4" t="s">
         <v>125</v>
@@ -73231,7 +73231,7 @@
       </c>
       <c r="Y810" s="4"/>
       <c r="Z810" s="4" t="s">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="AA810" s="4" t="s">
         <v>48</v>
@@ -73269,24 +73269,24 @@
         <v>1690</v>
       </c>
       <c r="J811" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K811" s="4"/>
       <c r="L811" s="4" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="M811" s="4" t="s">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="N811" s="4">
         <v>46</v>
       </c>
       <c r="O811" s="4" t="s">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="P811" s="5"/>
       <c r="Q811" s="4" t="s">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="R811" s="4" t="s">
         <v>63</v>
@@ -73307,7 +73307,7 @@
       </c>
       <c r="Y811" s="4"/>
       <c r="Z811" s="4" t="s">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="AA811" s="4"/>
       <c r="AB811" s="4" t="s">
@@ -73343,11 +73343,11 @@
         <v>1690</v>
       </c>
       <c r="J812" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K812" s="4"/>
       <c r="L812" s="4" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="M812" s="4" t="s">
         <v>253</v>
@@ -73356,11 +73356,11 @@
         <v>39</v>
       </c>
       <c r="O812" s="4" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="P812" s="5"/>
       <c r="Q812" s="4" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="R812" s="4" t="s">
         <v>63</v>
@@ -73372,7 +73372,7 @@
         <v>0</v>
       </c>
       <c r="U812" s="4" t="s">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="V812" s="4" t="s">
         <v>1583</v>
@@ -73385,7 +73385,7 @@
       </c>
       <c r="Y812" s="4"/>
       <c r="Z812" s="4" t="s">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="AA812" s="4" t="s">
         <v>48</v>
@@ -73423,11 +73423,11 @@
         <v>1690</v>
       </c>
       <c r="J813" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K813" s="4"/>
       <c r="L813" s="4" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="M813" s="4" t="s">
         <v>253</v>
@@ -73436,11 +73436,11 @@
         <v>50</v>
       </c>
       <c r="O813" s="4" t="s">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="P813" s="5"/>
       <c r="Q813" s="4" t="s">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="R813" s="4" t="s">
         <v>63</v>
@@ -73452,10 +73452,10 @@
         <v>34</v>
       </c>
       <c r="U813" s="4" t="s">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="V813" s="4" t="s">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="W813" s="4">
         <v>13</v>
@@ -73465,7 +73465,7 @@
       </c>
       <c r="Y813" s="4"/>
       <c r="Z813" s="4" t="s">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="AA813" s="4" t="s">
         <v>488</v>
@@ -73503,11 +73503,11 @@
         <v>1690</v>
       </c>
       <c r="J814" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K814" s="4"/>
       <c r="L814" s="4" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="M814" s="4" t="s">
         <v>666</v>
@@ -73516,11 +73516,11 @@
         <v>50</v>
       </c>
       <c r="O814" s="4" t="s">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="P814" s="5"/>
       <c r="Q814" s="4" t="s">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="R814" s="4" t="s">
         <v>63</v>
@@ -73532,7 +73532,7 @@
         <v>0</v>
       </c>
       <c r="U814" s="4" t="s">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="V814" s="4" t="s">
         <v>125</v>
@@ -73545,7 +73545,7 @@
       </c>
       <c r="Y814" s="4"/>
       <c r="Z814" s="4" t="s">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="AA814" s="4" t="s">
         <v>48</v>
@@ -73583,7 +73583,7 @@
         <v>1690</v>
       </c>
       <c r="J815" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K815" s="4"/>
       <c r="L815" s="4" t="s">
@@ -73596,11 +73596,11 @@
         <v>18</v>
       </c>
       <c r="O815" s="4" t="s">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="P815" s="5"/>
       <c r="Q815" s="4" t="s">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="R815" s="4" t="s">
         <v>63</v>
@@ -73621,7 +73621,7 @@
       </c>
       <c r="Y815" s="4"/>
       <c r="Z815" s="4" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="AA815" s="4" t="s">
         <v>65</v>
@@ -73659,7 +73659,7 @@
         <v>1690</v>
       </c>
       <c r="J816" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K816" s="4"/>
       <c r="L816" s="4" t="s">
@@ -73672,11 +73672,11 @@
         <v>19</v>
       </c>
       <c r="O816" s="4" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="P816" s="5"/>
       <c r="Q816" s="4" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="R816" s="4" t="s">
         <v>56</v>
@@ -73697,7 +73697,7 @@
       </c>
       <c r="Y816" s="4"/>
       <c r="Z816" s="4" t="s">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="AA816" s="4" t="s">
         <v>48</v>
@@ -73735,7 +73735,7 @@
         <v>1690</v>
       </c>
       <c r="J817" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K817" s="4"/>
       <c r="L817" s="4" t="s">
@@ -73748,11 +73748,11 @@
         <v>46</v>
       </c>
       <c r="O817" s="4" t="s">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="P817" s="5"/>
       <c r="Q817" s="4" t="s">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="R817" s="4" t="s">
         <v>63</v>
@@ -73773,7 +73773,7 @@
       </c>
       <c r="Y817" s="4"/>
       <c r="Z817" s="4" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="AA817" s="4" t="s">
         <v>65</v>
@@ -73811,7 +73811,7 @@
         <v>1690</v>
       </c>
       <c r="J818" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K818" s="4"/>
       <c r="L818" s="4" t="s">
@@ -73824,11 +73824,11 @@
         <v>13</v>
       </c>
       <c r="O818" s="4" t="s">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="P818" s="5"/>
       <c r="Q818" s="4" t="s">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="R818" s="4" t="s">
         <v>56</v>
@@ -73849,7 +73849,7 @@
       </c>
       <c r="Y818" s="4"/>
       <c r="Z818" s="4" t="s">
-        <v>3122</v>
+        <v>3123</v>
       </c>
       <c r="AA818" s="4" t="s">
         <v>48</v>
@@ -73887,7 +73887,7 @@
         <v>1690</v>
       </c>
       <c r="J819" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K819" s="4"/>
       <c r="L819" s="4" t="s">
@@ -73900,11 +73900,11 @@
         <v>31</v>
       </c>
       <c r="O819" s="4" t="s">
-        <v>3123</v>
+        <v>3124</v>
       </c>
       <c r="P819" s="5"/>
       <c r="Q819" s="4" t="s">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="R819" s="4" t="s">
         <v>56</v>
@@ -73916,7 +73916,7 @@
         <v>0</v>
       </c>
       <c r="U819" s="4" t="s">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="V819" s="4" t="s">
         <v>82</v>
@@ -73929,7 +73929,7 @@
       </c>
       <c r="Y819" s="4"/>
       <c r="Z819" s="4" t="s">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="AA819" s="4" t="s">
         <v>65</v>
@@ -73967,7 +73967,7 @@
         <v>1690</v>
       </c>
       <c r="J820" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K820" s="4"/>
       <c r="L820" s="4" t="s">
@@ -73980,11 +73980,11 @@
         <v>84</v>
       </c>
       <c r="O820" s="4" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="P820" s="5"/>
       <c r="Q820" s="4" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="R820" s="4" t="s">
         <v>63</v>
@@ -73996,7 +73996,7 @@
         <v>0</v>
       </c>
       <c r="U820" s="4" t="s">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="V820" s="4" t="s">
         <v>941</v>
@@ -74009,7 +74009,7 @@
       </c>
       <c r="Y820" s="4"/>
       <c r="Z820" s="4" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="AA820" s="4" t="s">
         <v>65</v>
@@ -74047,7 +74047,7 @@
         <v>1690</v>
       </c>
       <c r="J821" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K821" s="4"/>
       <c r="L821" s="4" t="s">
@@ -74060,11 +74060,11 @@
         <v>27</v>
       </c>
       <c r="O821" s="4" t="s">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="P821" s="5"/>
       <c r="Q821" s="4" t="s">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="R821" s="4" t="s">
         <v>56</v>
@@ -74085,7 +74085,7 @@
       </c>
       <c r="Y821" s="4"/>
       <c r="Z821" s="4" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="AA821" s="4" t="s">
         <v>65</v>
@@ -74123,22 +74123,22 @@
         <v>1690</v>
       </c>
       <c r="J822" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K822" s="4"/>
       <c r="L822" s="4" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="M822" s="4" t="s">
         <v>1787</v>
       </c>
       <c r="N822" s="4"/>
       <c r="O822" s="4" t="s">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="P822" s="5"/>
       <c r="Q822" s="4" t="s">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="R822" s="4" t="s">
         <v>63</v>
@@ -74159,7 +74159,7 @@
       </c>
       <c r="Y822" s="4"/>
       <c r="Z822" s="4" t="s">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="AA822" s="4" t="s">
         <v>48</v>
@@ -74197,22 +74197,22 @@
         <v>1690</v>
       </c>
       <c r="J823" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K823" s="4"/>
       <c r="L823" s="4" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="M823" s="4" t="s">
         <v>2471</v>
       </c>
       <c r="N823" s="4"/>
       <c r="O823" s="4" t="s">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="P823" s="5"/>
       <c r="Q823" s="4" t="s">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="R823" s="4" t="s">
         <v>63</v>
@@ -74233,7 +74233,7 @@
       </c>
       <c r="Y823" s="4"/>
       <c r="Z823" s="4" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="AA823" s="4" t="s">
         <v>65</v>
@@ -74271,22 +74271,22 @@
         <v>1690</v>
       </c>
       <c r="J824" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K824" s="4"/>
       <c r="L824" s="4" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="M824" s="4" t="s">
         <v>459</v>
       </c>
       <c r="N824" s="4"/>
       <c r="O824" s="4" t="s">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="P824" s="5"/>
       <c r="Q824" s="4" t="s">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="R824" s="4" t="s">
         <v>63</v>
@@ -74307,7 +74307,7 @@
       </c>
       <c r="Y824" s="4"/>
       <c r="Z824" s="4" t="s">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="AA824" s="4"/>
       <c r="AB824" s="4" t="s">
@@ -74343,22 +74343,22 @@
         <v>1690</v>
       </c>
       <c r="J825" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K825" s="4"/>
       <c r="L825" s="4" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="M825" s="4" t="s">
         <v>459</v>
       </c>
       <c r="N825" s="4"/>
       <c r="O825" s="4" t="s">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="P825" s="5"/>
       <c r="Q825" s="4" t="s">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="R825" s="4" t="s">
         <v>63</v>
@@ -74370,7 +74370,7 @@
         <v>0</v>
       </c>
       <c r="U825" s="4" t="s">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="V825" s="4" t="s">
         <v>317</v>
@@ -74383,7 +74383,7 @@
       </c>
       <c r="Y825" s="4"/>
       <c r="Z825" s="4" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="AA825" s="4" t="s">
         <v>65</v>
@@ -74421,7 +74421,7 @@
         <v>1690</v>
       </c>
       <c r="J826" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K826" s="4"/>
       <c r="L826" s="4" t="s">
@@ -74434,11 +74434,11 @@
         <v>29</v>
       </c>
       <c r="O826" s="4" t="s">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="P826" s="5"/>
       <c r="Q826" s="4" t="s">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="R826" s="4" t="s">
         <v>63</v>
@@ -74450,7 +74450,7 @@
         <v>71</v>
       </c>
       <c r="U826" s="4" t="s">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="V826" s="4" t="s">
         <v>75</v>
@@ -74463,7 +74463,7 @@
       </c>
       <c r="Y826" s="4"/>
       <c r="Z826" s="4" t="s">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="AA826" s="4" t="s">
         <v>48</v>
@@ -74501,7 +74501,7 @@
         <v>1690</v>
       </c>
       <c r="J827" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K827" s="4"/>
       <c r="L827" s="4" t="s">
@@ -74514,11 +74514,11 @@
         <v>21</v>
       </c>
       <c r="O827" s="4" t="s">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="P827" s="5"/>
       <c r="Q827" s="4" t="s">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="R827" s="4" t="s">
         <v>63</v>
@@ -74530,7 +74530,7 @@
         <v>70</v>
       </c>
       <c r="U827" s="4" t="s">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="V827" s="4" t="s">
         <v>317</v>
@@ -74543,7 +74543,7 @@
       </c>
       <c r="Y827" s="4"/>
       <c r="Z827" s="4" t="s">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="AA827" s="4" t="s">
         <v>48</v>
@@ -74581,7 +74581,7 @@
         <v>1690</v>
       </c>
       <c r="J828" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K828" s="4"/>
       <c r="L828" s="4" t="s">
@@ -74594,11 +74594,11 @@
         <v>75</v>
       </c>
       <c r="O828" s="4" t="s">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="P828" s="5"/>
       <c r="Q828" s="4" t="s">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="R828" s="4" t="s">
         <v>63</v>
@@ -74619,7 +74619,7 @@
       </c>
       <c r="Y828" s="4"/>
       <c r="Z828" s="4" t="s">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="AA828" s="4" t="s">
         <v>65</v>
@@ -74657,7 +74657,7 @@
         <v>1690</v>
       </c>
       <c r="J829" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K829" s="4"/>
       <c r="L829" s="4" t="s">
@@ -74670,11 +74670,11 @@
         <v>40</v>
       </c>
       <c r="O829" s="4" t="s">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="P829" s="5"/>
       <c r="Q829" s="4" t="s">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="R829" s="4" t="s">
         <v>63</v>
@@ -74686,7 +74686,7 @@
         <v>0</v>
       </c>
       <c r="U829" s="4" t="s">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="V829" s="4" t="s">
         <v>125</v>
@@ -74699,7 +74699,7 @@
       </c>
       <c r="Y829" s="4"/>
       <c r="Z829" s="4" t="s">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="AA829" s="4" t="s">
         <v>48</v>
@@ -74737,7 +74737,7 @@
         <v>1690</v>
       </c>
       <c r="J830" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K830" s="4"/>
       <c r="L830" s="4" t="s">
@@ -74748,11 +74748,11 @@
       </c>
       <c r="N830" s="4"/>
       <c r="O830" s="4" t="s">
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="P830" s="5"/>
       <c r="Q830" s="4" t="s">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="R830" s="4" t="s">
         <v>63</v>
@@ -74773,7 +74773,7 @@
       </c>
       <c r="Y830" s="4"/>
       <c r="Z830" s="4" t="s">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="AA830" s="4"/>
       <c r="AB830" s="4" t="s">
@@ -74809,7 +74809,7 @@
         <v>1690</v>
       </c>
       <c r="J831" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K831" s="4"/>
       <c r="L831" s="4" t="s">
@@ -74822,11 +74822,11 @@
         <v>94</v>
       </c>
       <c r="O831" s="4" t="s">
-        <v>3162</v>
+        <v>3163</v>
       </c>
       <c r="P831" s="5"/>
       <c r="Q831" s="4" t="s">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="R831" s="4" t="s">
         <v>63</v>
@@ -74838,7 +74838,7 @@
         <v>0</v>
       </c>
       <c r="U831" s="4" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="V831" s="4" t="s">
         <v>89</v>
@@ -74851,7 +74851,7 @@
       </c>
       <c r="Y831" s="4"/>
       <c r="Z831" s="4" t="s">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="AA831" s="4" t="s">
         <v>48</v>
@@ -74889,24 +74889,24 @@
         <v>1690</v>
       </c>
       <c r="J832" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K832" s="4"/>
       <c r="L832" s="4" t="s">
         <v>305</v>
       </c>
       <c r="M832" s="4" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="N832" s="4">
         <v>6</v>
       </c>
       <c r="O832" s="4" t="s">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="P832" s="5"/>
       <c r="Q832" s="4" t="s">
-        <v>3167</v>
+        <v>3168</v>
       </c>
       <c r="R832" s="4" t="s">
         <v>63</v>
@@ -74927,7 +74927,7 @@
       </c>
       <c r="Y832" s="4"/>
       <c r="Z832" s="4" t="s">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="AA832" s="4" t="s">
         <v>65</v>
@@ -74965,7 +74965,7 @@
         <v>1690</v>
       </c>
       <c r="J833" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K833" s="4"/>
       <c r="L833" s="4" t="s">
@@ -74976,11 +74976,11 @@
       </c>
       <c r="N833" s="4"/>
       <c r="O833" s="4" t="s">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="P833" s="5"/>
       <c r="Q833" s="4" t="s">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="R833" s="4" t="s">
         <v>56</v>
@@ -74992,7 +74992,7 @@
         <v>69</v>
       </c>
       <c r="U833" s="4" t="s">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="V833" s="4" t="s">
         <v>317</v>
@@ -75005,7 +75005,7 @@
       </c>
       <c r="Y833" s="4"/>
       <c r="Z833" s="4" t="s">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="AA833" s="4" t="s">
         <v>48</v>
@@ -75043,7 +75043,7 @@
         <v>1690</v>
       </c>
       <c r="J834" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K834" s="4"/>
       <c r="L834" s="4" t="s">
@@ -75054,11 +75054,11 @@
       </c>
       <c r="N834" s="4"/>
       <c r="O834" s="4" t="s">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="P834" s="5"/>
       <c r="Q834" s="4" t="s">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="R834" s="4" t="s">
         <v>56</v>
@@ -75079,7 +75079,7 @@
       </c>
       <c r="Y834" s="4"/>
       <c r="Z834" s="4" t="s">
-        <v>3175</v>
+        <v>3176</v>
       </c>
       <c r="AA834" s="4" t="s">
         <v>48</v>
@@ -75117,7 +75117,7 @@
         <v>1690</v>
       </c>
       <c r="J835" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K835" s="4"/>
       <c r="L835" s="4" t="s">
@@ -75130,11 +75130,11 @@
         <v>41</v>
       </c>
       <c r="O835" s="4" t="s">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="P835" s="5"/>
       <c r="Q835" s="4" t="s">
-        <v>3177</v>
+        <v>3178</v>
       </c>
       <c r="R835" s="4" t="s">
         <v>56</v>
@@ -75155,7 +75155,7 @@
       </c>
       <c r="Y835" s="4"/>
       <c r="Z835" s="4" t="s">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="AA835" s="4"/>
       <c r="AB835" s="4" t="s">
@@ -75191,7 +75191,7 @@
         <v>1690</v>
       </c>
       <c r="J836" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K836" s="4"/>
       <c r="L836" s="4" t="s">
@@ -75204,11 +75204,11 @@
         <v>7</v>
       </c>
       <c r="O836" s="4" t="s">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="P836" s="5"/>
       <c r="Q836" s="4" t="s">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="R836" s="4" t="s">
         <v>56</v>
@@ -75229,7 +75229,7 @@
       </c>
       <c r="Y836" s="4"/>
       <c r="Z836" s="4" t="s">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="AA836" s="4" t="s">
         <v>65</v>
@@ -75267,22 +75267,22 @@
         <v>1690</v>
       </c>
       <c r="J837" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K837" s="4"/>
       <c r="L837" s="4" t="s">
         <v>253</v>
       </c>
       <c r="M837" s="4" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="N837" s="4"/>
       <c r="O837" s="4" t="s">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="P837" s="5"/>
       <c r="Q837" s="4" t="s">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="R837" s="4" t="s">
         <v>56</v>
@@ -75294,7 +75294,7 @@
         <v>0</v>
       </c>
       <c r="U837" s="4" t="s">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="V837" s="4" t="s">
         <v>363</v>
@@ -75307,7 +75307,7 @@
       </c>
       <c r="Y837" s="4"/>
       <c r="Z837" s="4" t="s">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="AA837" s="4" t="s">
         <v>48</v>
@@ -75345,22 +75345,22 @@
         <v>1690</v>
       </c>
       <c r="J838" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K838" s="4"/>
       <c r="L838" s="4" t="s">
         <v>253</v>
       </c>
       <c r="M838" s="4" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="N838" s="4"/>
       <c r="O838" s="4" t="s">
-        <v>3186</v>
+        <v>3187</v>
       </c>
       <c r="P838" s="5"/>
       <c r="Q838" s="4" t="s">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="R838" s="4" t="s">
         <v>63</v>
@@ -75381,7 +75381,7 @@
       </c>
       <c r="Y838" s="4"/>
       <c r="Z838" s="4" t="s">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="AA838" s="4" t="s">
         <v>65</v>
@@ -75419,7 +75419,7 @@
         <v>1690</v>
       </c>
       <c r="J839" s="4" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="K839" s="4"/>
       <c r="L839" s="4" t="s">
@@ -75432,11 +75432,11 @@
         <v>10</v>
       </c>
       <c r="O839" s="4" t="s">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="P839" s="5"/>
       <c r="Q839" s="4" t="s">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="R839" s="4" t="s">
         <v>63</v>
@@ -75448,7 +75448,7 @@
         <v>0</v>
       </c>
       <c r="U839" s="4" t="s">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="V839" s="4" t="s">
         <v>317</v>
@@ -75461,7 +75461,7 @@
       </c>
       <c r="Y839" s="4"/>
       <c r="Z839" s="4" t="s">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="AA839" s="4" t="s">
         <v>48</v>
@@ -75499,24 +75499,24 @@
         <v>1690</v>
       </c>
       <c r="J840" s="4" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="K840" s="4"/>
       <c r="L840" s="4" t="s">
         <v>275</v>
       </c>
       <c r="M840" s="4" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="N840" s="4">
         <v>109</v>
       </c>
       <c r="O840" s="4" t="s">
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="P840" s="5"/>
       <c r="Q840" s="4" t="s">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="R840" s="4" t="s">
         <v>63</v>
@@ -75537,7 +75537,7 @@
       </c>
       <c r="Y840" s="4"/>
       <c r="Z840" s="4" t="s">
-        <v>3197</v>
+        <v>3198</v>
       </c>
       <c r="AA840" s="4" t="s">
         <v>65</v>
@@ -75575,24 +75575,24 @@
         <v>1690</v>
       </c>
       <c r="J841" s="4" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="K841" s="4"/>
       <c r="L841" s="4" t="s">
         <v>275</v>
       </c>
       <c r="M841" s="4" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="N841" s="4">
         <v>44</v>
       </c>
       <c r="O841" s="4" t="s">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="P841" s="5"/>
       <c r="Q841" s="4" t="s">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="R841" s="4" t="s">
         <v>56</v>
@@ -75651,24 +75651,24 @@
         <v>1690</v>
       </c>
       <c r="J842" s="4" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="K842" s="4"/>
       <c r="L842" s="4" t="s">
         <v>280</v>
       </c>
       <c r="M842" s="4" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="N842" s="4">
         <v>103</v>
       </c>
       <c r="O842" s="4" t="s">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="P842" s="5"/>
       <c r="Q842" s="4" t="s">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="R842" s="4" t="s">
         <v>63</v>
@@ -75689,7 +75689,7 @@
       </c>
       <c r="Y842" s="4"/>
       <c r="Z842" s="4" t="s">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="AA842" s="4" t="s">
         <v>48</v>
@@ -75727,24 +75727,24 @@
         <v>1690</v>
       </c>
       <c r="J843" s="4" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="K843" s="4"/>
       <c r="L843" s="4" t="s">
         <v>280</v>
       </c>
       <c r="M843" s="4" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="N843" s="4">
         <v>109</v>
       </c>
       <c r="O843" s="4" t="s">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="P843" s="5"/>
       <c r="Q843" s="4" t="s">
-        <v>3204</v>
+        <v>3205</v>
       </c>
       <c r="R843" s="4" t="s">
         <v>63</v>
@@ -75765,7 +75765,7 @@
       </c>
       <c r="Y843" s="4"/>
       <c r="Z843" s="4" t="s">
-        <v>3205</v>
+        <v>3206</v>
       </c>
       <c r="AA843" s="4" t="s">
         <v>48</v>
@@ -75803,11 +75803,11 @@
         <v>1690</v>
       </c>
       <c r="J844" s="4" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="K844" s="4"/>
       <c r="L844" s="4" t="s">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="M844" s="4" t="s">
         <v>59</v>
@@ -75816,11 +75816,11 @@
         <v>28</v>
       </c>
       <c r="O844" s="4" t="s">
-        <v>3207</v>
+        <v>3208</v>
       </c>
       <c r="P844" s="5"/>
       <c r="Q844" s="4" t="s">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="R844" s="4" t="s">
         <v>63</v>
@@ -75841,7 +75841,7 @@
       </c>
       <c r="Y844" s="4"/>
       <c r="Z844" s="4" t="s">
-        <v>3209</v>
+        <v>3210</v>
       </c>
       <c r="AA844" s="4"/>
       <c r="AB844" s="4" t="s">
@@ -75877,18 +75877,18 @@
         <v>2058</v>
       </c>
       <c r="J845" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K845" s="4"/>
       <c r="L845" s="4"/>
       <c r="M845" s="4"/>
       <c r="N845" s="4"/>
       <c r="O845" s="4" t="s">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="P845" s="5"/>
       <c r="Q845" s="4" t="s">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="R845" s="4" t="s">
         <v>63</v>
@@ -75909,7 +75909,7 @@
       </c>
       <c r="Y845" s="4"/>
       <c r="Z845" s="4" t="s">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="AA845" s="4"/>
       <c r="AB845" s="4" t="s">
@@ -75945,18 +75945,18 @@
         <v>2058</v>
       </c>
       <c r="J846" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K846" s="4"/>
       <c r="L846" s="4"/>
       <c r="M846" s="4"/>
       <c r="N846" s="4"/>
       <c r="O846" s="4" t="s">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="P846" s="5"/>
       <c r="Q846" s="4" t="s">
-        <v>3215</v>
+        <v>3216</v>
       </c>
       <c r="R846" s="4" t="s">
         <v>63</v>
@@ -75977,7 +75977,7 @@
       </c>
       <c r="Y846" s="4"/>
       <c r="Z846" s="4" t="s">
-        <v>3216</v>
+        <v>3217</v>
       </c>
       <c r="AA846" s="4"/>
       <c r="AB846" s="4" t="s">
@@ -76013,18 +76013,18 @@
         <v>2058</v>
       </c>
       <c r="J847" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K847" s="4"/>
       <c r="L847" s="4"/>
       <c r="M847" s="4"/>
       <c r="N847" s="4"/>
       <c r="O847" s="4" t="s">
-        <v>3217</v>
+        <v>3218</v>
       </c>
       <c r="P847" s="5"/>
       <c r="Q847" s="4" t="s">
-        <v>3218</v>
+        <v>3219</v>
       </c>
       <c r="R847" s="4" t="s">
         <v>63</v>
@@ -76045,7 +76045,7 @@
       </c>
       <c r="Y847" s="4"/>
       <c r="Z847" s="4" t="s">
-        <v>3219</v>
+        <v>3220</v>
       </c>
       <c r="AA847" s="4"/>
       <c r="AB847" s="4" t="s">
@@ -76081,18 +76081,18 @@
         <v>2058</v>
       </c>
       <c r="J848" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K848" s="4"/>
       <c r="L848" s="4"/>
       <c r="M848" s="4"/>
       <c r="N848" s="4"/>
       <c r="O848" s="4" t="s">
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="P848" s="5"/>
       <c r="Q848" s="4" t="s">
-        <v>3221</v>
+        <v>3222</v>
       </c>
       <c r="R848" s="4" t="s">
         <v>63</v>
@@ -76113,7 +76113,7 @@
       </c>
       <c r="Y848" s="4"/>
       <c r="Z848" s="4" t="s">
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="AA848" s="4"/>
       <c r="AB848" s="4" t="s">
@@ -76149,18 +76149,18 @@
         <v>2058</v>
       </c>
       <c r="J849" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K849" s="4"/>
       <c r="L849" s="4"/>
       <c r="M849" s="4"/>
       <c r="N849" s="4"/>
       <c r="O849" s="4" t="s">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="P849" s="5"/>
       <c r="Q849" s="4" t="s">
-        <v>3224</v>
+        <v>3225</v>
       </c>
       <c r="R849" s="4" t="s">
         <v>63</v>
@@ -76181,7 +76181,7 @@
       </c>
       <c r="Y849" s="4"/>
       <c r="Z849" s="4" t="s">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="AA849" s="4"/>
       <c r="AB849" s="4" t="s">
@@ -76217,18 +76217,18 @@
         <v>2058</v>
       </c>
       <c r="J850" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K850" s="4"/>
       <c r="L850" s="4"/>
       <c r="M850" s="4"/>
       <c r="N850" s="4"/>
       <c r="O850" s="4" t="s">
-        <v>3226</v>
+        <v>3227</v>
       </c>
       <c r="P850" s="5"/>
       <c r="Q850" s="4" t="s">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="R850" s="4" t="s">
         <v>63</v>
@@ -76249,7 +76249,7 @@
       </c>
       <c r="Y850" s="4"/>
       <c r="Z850" s="4" t="s">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="AA850" s="4"/>
       <c r="AB850" s="4" t="s">
@@ -76285,18 +76285,18 @@
         <v>1690</v>
       </c>
       <c r="J851" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K851" s="4"/>
       <c r="L851" s="4"/>
       <c r="M851" s="4"/>
       <c r="N851" s="4"/>
       <c r="O851" s="4" t="s">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="P851" s="5"/>
       <c r="Q851" s="4" t="s">
-        <v>3229</v>
+        <v>3230</v>
       </c>
       <c r="R851" s="4" t="s">
         <v>63</v>
@@ -76317,7 +76317,7 @@
       </c>
       <c r="Y851" s="4"/>
       <c r="Z851" s="4" t="s">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="AA851" s="4"/>
       <c r="AB851" s="4" t="s">
@@ -76353,18 +76353,18 @@
         <v>2058</v>
       </c>
       <c r="J852" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K852" s="4"/>
       <c r="L852" s="4"/>
       <c r="M852" s="4"/>
       <c r="N852" s="4"/>
       <c r="O852" s="4" t="s">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="P852" s="5"/>
       <c r="Q852" s="4" t="s">
-        <v>3232</v>
+        <v>3233</v>
       </c>
       <c r="R852" s="4" t="s">
         <v>63</v>
@@ -76385,7 +76385,7 @@
       </c>
       <c r="Y852" s="4"/>
       <c r="Z852" s="4" t="s">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="AA852" s="4"/>
       <c r="AB852" s="4" t="s">
@@ -76421,18 +76421,18 @@
         <v>2058</v>
       </c>
       <c r="J853" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K853" s="4"/>
       <c r="L853" s="4"/>
       <c r="M853" s="4"/>
       <c r="N853" s="4"/>
       <c r="O853" s="4" t="s">
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="P853" s="5"/>
       <c r="Q853" s="4" t="s">
-        <v>3235</v>
+        <v>3236</v>
       </c>
       <c r="R853" s="4" t="s">
         <v>63</v>
@@ -76453,7 +76453,7 @@
       </c>
       <c r="Y853" s="4"/>
       <c r="Z853" s="4" t="s">
-        <v>3236</v>
+        <v>3237</v>
       </c>
       <c r="AA853" s="4"/>
       <c r="AB853" s="4" t="s">
@@ -76489,18 +76489,18 @@
         <v>2058</v>
       </c>
       <c r="J854" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K854" s="4"/>
       <c r="L854" s="4"/>
       <c r="M854" s="4"/>
       <c r="N854" s="4"/>
       <c r="O854" s="4" t="s">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="P854" s="5"/>
       <c r="Q854" s="4" t="s">
-        <v>3238</v>
+        <v>3239</v>
       </c>
       <c r="R854" s="4" t="s">
         <v>63</v>
@@ -76521,7 +76521,7 @@
       </c>
       <c r="Y854" s="4"/>
       <c r="Z854" s="4" t="s">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="AA854" s="4"/>
       <c r="AB854" s="4" t="s">
@@ -76557,18 +76557,18 @@
         <v>2058</v>
       </c>
       <c r="J855" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K855" s="4"/>
       <c r="L855" s="4"/>
       <c r="M855" s="4"/>
       <c r="N855" s="4"/>
       <c r="O855" s="4" t="s">
-        <v>3240</v>
+        <v>3241</v>
       </c>
       <c r="P855" s="5"/>
       <c r="Q855" s="4" t="s">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="R855" s="4" t="s">
         <v>63</v>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="Y855" s="4"/>
       <c r="Z855" s="4" t="s">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="AA855" s="4"/>
       <c r="AB855" s="4" t="s">
@@ -76625,18 +76625,18 @@
         <v>2058</v>
       </c>
       <c r="J856" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K856" s="4"/>
       <c r="L856" s="4"/>
       <c r="M856" s="4"/>
       <c r="N856" s="4"/>
       <c r="O856" s="4" t="s">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="P856" s="5"/>
       <c r="Q856" s="4" t="s">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="R856" s="4" t="s">
         <v>63</v>
@@ -76657,7 +76657,7 @@
       </c>
       <c r="Y856" s="4"/>
       <c r="Z856" s="4" t="s">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="AA856" s="4"/>
       <c r="AB856" s="4" t="s">
@@ -76693,18 +76693,18 @@
         <v>2058</v>
       </c>
       <c r="J857" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K857" s="4"/>
       <c r="L857" s="4"/>
       <c r="M857" s="4"/>
       <c r="N857" s="4"/>
       <c r="O857" s="4" t="s">
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="P857" s="5"/>
       <c r="Q857" s="4" t="s">
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="R857" s="4" t="s">
         <v>63</v>
@@ -76725,7 +76725,7 @@
       </c>
       <c r="Y857" s="4"/>
       <c r="Z857" s="4" t="s">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="AA857" s="4"/>
       <c r="AB857" s="4" t="s">
@@ -76761,18 +76761,18 @@
         <v>2058</v>
       </c>
       <c r="J858" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K858" s="4"/>
       <c r="L858" s="4"/>
       <c r="M858" s="4"/>
       <c r="N858" s="4"/>
       <c r="O858" s="4" t="s">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="P858" s="5"/>
       <c r="Q858" s="4" t="s">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="R858" s="4" t="s">
         <v>63</v>
@@ -76793,7 +76793,7 @@
       </c>
       <c r="Y858" s="4"/>
       <c r="Z858" s="4" t="s">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="AA858" s="4"/>
       <c r="AB858" s="4" t="s">
@@ -76829,18 +76829,18 @@
         <v>2058</v>
       </c>
       <c r="J859" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K859" s="4"/>
       <c r="L859" s="4"/>
       <c r="M859" s="4"/>
       <c r="N859" s="4"/>
       <c r="O859" s="4" t="s">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="P859" s="5"/>
       <c r="Q859" s="4" t="s">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="R859" s="4" t="s">
         <v>63</v>
@@ -76861,7 +76861,7 @@
       </c>
       <c r="Y859" s="4"/>
       <c r="Z859" s="4" t="s">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="AA859" s="4"/>
       <c r="AB859" s="4" t="s">
@@ -76897,18 +76897,18 @@
         <v>2058</v>
       </c>
       <c r="J860" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K860" s="4"/>
       <c r="L860" s="4"/>
       <c r="M860" s="4"/>
       <c r="N860" s="4"/>
       <c r="O860" s="4" t="s">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="P860" s="5"/>
       <c r="Q860" s="4" t="s">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="R860" s="4" t="s">
         <v>63</v>
@@ -76929,7 +76929,7 @@
       </c>
       <c r="Y860" s="4"/>
       <c r="Z860" s="4" t="s">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="AA860" s="4"/>
       <c r="AB860" s="4" t="s">
@@ -76965,18 +76965,18 @@
         <v>1690</v>
       </c>
       <c r="J861" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K861" s="4"/>
       <c r="L861" s="4"/>
       <c r="M861" s="4"/>
       <c r="N861" s="4"/>
       <c r="O861" s="4" t="s">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="P861" s="5"/>
       <c r="Q861" s="4" t="s">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="R861" s="4" t="s">
         <v>63</v>
@@ -76997,7 +76997,7 @@
       </c>
       <c r="Y861" s="4"/>
       <c r="Z861" s="4" t="s">
-        <v>3260</v>
+        <v>3261</v>
       </c>
       <c r="AA861" s="4"/>
       <c r="AB861" s="4" t="s">
@@ -77033,18 +77033,18 @@
         <v>2058</v>
       </c>
       <c r="J862" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K862" s="4"/>
       <c r="L862" s="4"/>
       <c r="M862" s="4"/>
       <c r="N862" s="4"/>
       <c r="O862" s="4" t="s">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="P862" s="5"/>
       <c r="Q862" s="4" t="s">
-        <v>3262</v>
+        <v>3263</v>
       </c>
       <c r="R862" s="4" t="s">
         <v>63</v>
@@ -77065,7 +77065,7 @@
       </c>
       <c r="Y862" s="4"/>
       <c r="Z862" s="4" t="s">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="AA862" s="4"/>
       <c r="AB862" s="4" t="s">
@@ -77101,18 +77101,18 @@
         <v>2058</v>
       </c>
       <c r="J863" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K863" s="4"/>
       <c r="L863" s="4"/>
       <c r="M863" s="4"/>
       <c r="N863" s="4"/>
       <c r="O863" s="4" t="s">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="P863" s="5"/>
       <c r="Q863" s="4" t="s">
-        <v>3265</v>
+        <v>3266</v>
       </c>
       <c r="R863" s="4" t="s">
         <v>63</v>
@@ -77133,7 +77133,7 @@
       </c>
       <c r="Y863" s="4"/>
       <c r="Z863" s="4" t="s">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="AA863" s="4"/>
       <c r="AB863" s="4" t="s">
@@ -77169,18 +77169,18 @@
         <v>2058</v>
       </c>
       <c r="J864" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K864" s="4"/>
       <c r="L864" s="4"/>
       <c r="M864" s="4"/>
       <c r="N864" s="4"/>
       <c r="O864" s="4" t="s">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="P864" s="5"/>
       <c r="Q864" s="4" t="s">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="R864" s="4" t="s">
         <v>63</v>
@@ -77201,7 +77201,7 @@
       </c>
       <c r="Y864" s="4"/>
       <c r="Z864" s="4" t="s">
-        <v>3269</v>
+        <v>3270</v>
       </c>
       <c r="AA864" s="4"/>
       <c r="AB864" s="4" t="s">
@@ -77237,18 +77237,18 @@
         <v>2058</v>
       </c>
       <c r="J865" s="4" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="K865" s="4"/>
       <c r="L865" s="4"/>
       <c r="M865" s="4"/>
       <c r="N865" s="4"/>
       <c r="O865" s="4" t="s">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="P865" s="5"/>
       <c r="Q865" s="4" t="s">
-        <v>3271</v>
+        <v>3272</v>
       </c>
       <c r="R865" s="4" t="s">
         <v>63</v>
@@ -77269,7 +77269,7 @@
       </c>
       <c r="Y865" s="4"/>
       <c r="Z865" s="4" t="s">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="AA865" s="4"/>
       <c r="AB865" s="4" t="s">
@@ -77312,11 +77312,11 @@
       <c r="M866" s="4"/>
       <c r="N866" s="4"/>
       <c r="O866" s="4" t="s">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="P866" s="5"/>
       <c r="Q866" s="4" t="s">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="R866" s="4" t="s">
         <v>63</v>
@@ -77337,7 +77337,7 @@
       </c>
       <c r="Y866" s="4"/>
       <c r="Z866" s="4" t="s">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="AA866" s="4"/>
       <c r="AB866" s="4" t="s">
@@ -77380,11 +77380,11 @@
       <c r="M867" s="4"/>
       <c r="N867" s="4"/>
       <c r="O867" s="4" t="s">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="P867" s="5"/>
       <c r="Q867" s="4" t="s">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="R867" s="4" t="s">
         <v>63</v>
@@ -77405,7 +77405,7 @@
       </c>
       <c r="Y867" s="4"/>
       <c r="Z867" s="4" t="s">
-        <v>3278</v>
+        <v>3279</v>
       </c>
       <c r="AA867" s="4"/>
       <c r="AB867" s="4" t="s">
@@ -77448,17 +77448,17 @@
         <v>2255</v>
       </c>
       <c r="M868" s="4" t="s">
-        <v>3279</v>
+        <v>3280</v>
       </c>
       <c r="N868" s="4">
         <v>20</v>
       </c>
       <c r="O868" s="4" t="s">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="P868" s="5"/>
       <c r="Q868" s="4" t="s">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="R868" s="4" t="s">
         <v>56</v>
@@ -77479,7 +77479,7 @@
       </c>
       <c r="Y868" s="4"/>
       <c r="Z868" s="4" t="s">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="AA868" s="4"/>
       <c r="AB868" s="4" t="s">
@@ -77528,11 +77528,11 @@
         <v>3</v>
       </c>
       <c r="O869" s="4" t="s">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="P869" s="5"/>
       <c r="Q869" s="4" t="s">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="R869" s="4" t="s">
         <v>63</v>
@@ -77544,7 +77544,7 @@
         <v>14</v>
       </c>
       <c r="U869" s="4" t="s">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="V869" s="4" t="s">
         <v>198</v>
@@ -77557,7 +77557,7 @@
       </c>
       <c r="Y869" s="4"/>
       <c r="Z869" s="4" t="s">
-        <v>3286</v>
+        <v>3287</v>
       </c>
       <c r="AA869" s="4" t="s">
         <v>65</v>
@@ -77608,11 +77608,11 @@
         <v>61</v>
       </c>
       <c r="O870" s="4" t="s">
-        <v>3287</v>
+        <v>3288</v>
       </c>
       <c r="P870" s="5"/>
       <c r="Q870" s="4" t="s">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="R870" s="4" t="s">
         <v>43</v>
@@ -77633,7 +77633,7 @@
       </c>
       <c r="Y870" s="4"/>
       <c r="Z870" s="4" t="s">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="AA870" s="4" t="s">
         <v>65</v>
@@ -77675,7 +77675,7 @@
       </c>
       <c r="K871" s="4"/>
       <c r="L871" s="4" t="s">
-        <v>3290</v>
+        <v>3291</v>
       </c>
       <c r="M871" s="4" t="s">
         <v>345</v>
@@ -77684,11 +77684,11 @@
         <v>10</v>
       </c>
       <c r="O871" s="4" t="s">
-        <v>3291</v>
+        <v>3292</v>
       </c>
       <c r="P871" s="5"/>
       <c r="Q871" s="4" t="s">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="R871" s="4" t="s">
         <v>56</v>
@@ -77709,7 +77709,7 @@
       </c>
       <c r="Y871" s="4"/>
       <c r="Z871" s="4" t="s">
-        <v>3293</v>
+        <v>3294</v>
       </c>
       <c r="AA871" s="4" t="s">
         <v>48</v>
@@ -77760,11 +77760,11 @@
         <v>61</v>
       </c>
       <c r="O872" s="4" t="s">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="P872" s="5"/>
       <c r="Q872" s="4" t="s">
-        <v>3295</v>
+        <v>3296</v>
       </c>
       <c r="R872" s="4" t="s">
         <v>56</v>
@@ -77785,7 +77785,7 @@
       </c>
       <c r="Y872" s="4"/>
       <c r="Z872" s="4" t="s">
-        <v>3296</v>
+        <v>3297</v>
       </c>
       <c r="AA872" s="4" t="s">
         <v>182</v>
@@ -77836,11 +77836,11 @@
         <v>146</v>
       </c>
       <c r="O873" s="4" t="s">
-        <v>3297</v>
+        <v>3298</v>
       </c>
       <c r="P873" s="5"/>
       <c r="Q873" s="4" t="s">
-        <v>3298</v>
+        <v>3299</v>
       </c>
       <c r="R873" s="4" t="s">
         <v>56</v>
@@ -77852,7 +77852,7 @@
         <v>0</v>
       </c>
       <c r="U873" s="4" t="s">
-        <v>3299</v>
+        <v>3300</v>
       </c>
       <c r="V873" s="4" t="s">
         <v>208</v>
@@ -77865,7 +77865,7 @@
       </c>
       <c r="Y873" s="4"/>
       <c r="Z873" s="4" t="s">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="AA873" s="4" t="s">
         <v>65</v>
@@ -77916,11 +77916,11 @@
         <v>64</v>
       </c>
       <c r="O874" s="4" t="s">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="P874" s="5"/>
       <c r="Q874" s="4" t="s">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="R874" s="4" t="s">
         <v>56</v>
@@ -77932,7 +77932,7 @@
         <v>1</v>
       </c>
       <c r="U874" s="4" t="s">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="V874" s="4" t="s">
         <v>317</v>
@@ -77945,7 +77945,7 @@
       </c>
       <c r="Y874" s="4"/>
       <c r="Z874" s="4" t="s">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="AA874" s="4" t="s">
         <v>77</v>
@@ -77996,11 +77996,11 @@
         <v>118</v>
       </c>
       <c r="O875" s="4" t="s">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="P875" s="5"/>
       <c r="Q875" s="4" t="s">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="R875" s="4" t="s">
         <v>56</v>
@@ -78012,7 +78012,7 @@
         <v>56</v>
       </c>
       <c r="U875" s="4" t="s">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="V875" s="4" t="s">
         <v>317</v>
@@ -78025,7 +78025,7 @@
       </c>
       <c r="Y875" s="4"/>
       <c r="Z875" s="4" t="s">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="AA875" s="4" t="s">
         <v>48</v>
@@ -78076,11 +78076,11 @@
         <v>52</v>
       </c>
       <c r="O876" s="4" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="P876" s="5"/>
       <c r="Q876" s="4" t="s">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="R876" s="4" t="s">
         <v>296</v>
@@ -78092,7 +78092,7 @@
         <v>0</v>
       </c>
       <c r="U876" s="4" t="s">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="V876" s="4" t="s">
         <v>198</v>
@@ -78105,7 +78105,7 @@
       </c>
       <c r="Y876" s="4"/>
       <c r="Z876" s="4" t="s">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="AA876" s="4" t="s">
         <v>65</v>
@@ -78143,22 +78143,22 @@
         <v>1690</v>
       </c>
       <c r="J877" s="4" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="K877" s="4"/>
       <c r="L877" s="4" t="s">
         <v>1838</v>
       </c>
       <c r="M877" s="4" t="s">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="N877" s="4"/>
       <c r="O877" s="4" t="s">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="P877" s="5"/>
       <c r="Q877" s="4" t="s">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="R877" s="4" t="s">
         <v>56</v>
@@ -78179,7 +78179,7 @@
       </c>
       <c r="Y877" s="4"/>
       <c r="Z877" s="4" t="s">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="AA877" s="4" t="s">
         <v>65</v>
@@ -78217,11 +78217,11 @@
         <v>1690</v>
       </c>
       <c r="J878" s="4" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="K878" s="4"/>
       <c r="L878" s="4" t="s">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="M878" s="4" t="s">
         <v>874</v>
@@ -78230,11 +78230,11 @@
         <v>38</v>
       </c>
       <c r="O878" s="4" t="s">
-        <v>3318</v>
+        <v>3319</v>
       </c>
       <c r="P878" s="5"/>
       <c r="Q878" s="4" t="s">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="R878" s="4" t="s">
         <v>56</v>
@@ -78246,7 +78246,7 @@
         <v>1</v>
       </c>
       <c r="U878" s="4" t="s">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="V878" s="4" t="s">
         <v>198</v>
@@ -78259,7 +78259,7 @@
       </c>
       <c r="Y878" s="4"/>
       <c r="Z878" s="4" t="s">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="AA878" s="4" t="s">
         <v>48</v>
@@ -78297,22 +78297,22 @@
         <v>1690</v>
       </c>
       <c r="J879" s="4" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="K879" s="4"/>
       <c r="L879" s="4" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="M879" s="4" t="s">
         <v>1846</v>
       </c>
       <c r="N879" s="4"/>
       <c r="O879" s="4" t="s">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="P879" s="5"/>
       <c r="Q879" s="4" t="s">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="R879" s="4" t="s">
         <v>56</v>
@@ -78333,7 +78333,7 @@
       </c>
       <c r="Y879" s="4"/>
       <c r="Z879" s="4" t="s">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="AA879" s="4" t="s">
         <v>65</v>
@@ -78371,7 +78371,7 @@
         <v>1690</v>
       </c>
       <c r="J880" s="4" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="K880" s="4"/>
       <c r="L880" s="4" t="s">
@@ -78384,11 +78384,11 @@
         <v>125</v>
       </c>
       <c r="O880" s="4" t="s">
-        <v>3327</v>
+        <v>3328</v>
       </c>
       <c r="P880" s="5"/>
       <c r="Q880" s="4" t="s">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="R880" s="4" t="s">
         <v>56</v>
@@ -78400,10 +78400,10 @@
         <v>0</v>
       </c>
       <c r="U880" s="4" t="s">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="V880" s="4" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="W880" s="4">
         <v>13</v>
@@ -78413,7 +78413,7 @@
       </c>
       <c r="Y880" s="4"/>
       <c r="Z880" s="4" t="s">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="AA880" s="4" t="s">
         <v>65</v>
@@ -78451,22 +78451,22 @@
         <v>1690</v>
       </c>
       <c r="J881" s="4" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="K881" s="4"/>
       <c r="L881" s="4" t="s">
         <v>670</v>
       </c>
       <c r="M881" s="4" t="s">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="N881" s="4"/>
       <c r="O881" s="4" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="P881" s="5"/>
       <c r="Q881" s="4" t="s">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="R881" s="4" t="s">
         <v>63</v>
@@ -78478,7 +78478,7 @@
         <v>0</v>
       </c>
       <c r="U881" s="4" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="V881" s="4" t="s">
         <v>125</v>
@@ -78491,7 +78491,7 @@
       </c>
       <c r="Y881" s="4"/>
       <c r="Z881" s="4" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="AA881" s="4" t="s">
         <v>65</v>
@@ -78529,7 +78529,7 @@
         <v>1690</v>
       </c>
       <c r="J882" s="4" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="K882" s="4"/>
       <c r="L882" s="4" t="s">
@@ -78542,11 +78542,11 @@
         <v>44</v>
       </c>
       <c r="O882" s="4" t="s">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="P882" s="5"/>
       <c r="Q882" s="4" t="s">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="R882" s="4" t="s">
         <v>56</v>
@@ -78558,7 +78558,7 @@
         <v>1</v>
       </c>
       <c r="U882" s="4" t="s">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="V882" s="4" t="s">
         <v>203</v>
@@ -78571,7 +78571,7 @@
       </c>
       <c r="Y882" s="4"/>
       <c r="Z882" s="4" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="AA882" s="4" t="s">
         <v>182</v>
@@ -78616,17 +78616,17 @@
         <v>936</v>
       </c>
       <c r="M883" s="4" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="N883" s="4">
         <v>47</v>
       </c>
       <c r="O883" s="4" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="P883" s="5"/>
       <c r="Q883" s="4" t="s">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="R883" s="4" t="s">
         <v>56</v>
@@ -78638,7 +78638,7 @@
         <v>0</v>
       </c>
       <c r="U883" s="4" t="s">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="V883" s="4" t="s">
         <v>198</v>
@@ -78651,7 +78651,7 @@
       </c>
       <c r="Y883" s="4"/>
       <c r="Z883" s="4" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="AA883" s="4" t="s">
         <v>48</v>
@@ -78702,11 +78702,11 @@
         <v>1</v>
       </c>
       <c r="O884" s="4" t="s">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="P884" s="5"/>
       <c r="Q884" s="4" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="R884" s="4" t="s">
         <v>56</v>
@@ -78718,7 +78718,7 @@
         <v>0</v>
       </c>
       <c r="U884" s="4" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="V884" s="4" t="s">
         <v>125</v>
@@ -78731,7 +78731,7 @@
       </c>
       <c r="Y884" s="4"/>
       <c r="Z884" s="4" t="s">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="AA884" s="4" t="s">
         <v>65</v>
@@ -78782,11 +78782,11 @@
         <v>117</v>
       </c>
       <c r="O885" s="4" t="s">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="P885" s="5"/>
       <c r="Q885" s="4" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="R885" s="4" t="s">
         <v>63</v>
@@ -78798,7 +78798,7 @@
         <v>1</v>
       </c>
       <c r="U885" s="4" t="s">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="V885" s="4" t="s">
         <v>125</v>
@@ -78811,7 +78811,7 @@
       </c>
       <c r="Y885" s="4"/>
       <c r="Z885" s="4" t="s">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="AA885" s="4" t="s">
         <v>65</v>
@@ -78862,11 +78862,11 @@
         <v>117</v>
       </c>
       <c r="O886" s="4" t="s">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="P886" s="5"/>
       <c r="Q886" s="4" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="R886" s="4" t="s">
         <v>56</v>
@@ -78878,7 +78878,7 @@
         <v>0</v>
       </c>
       <c r="U886" s="4" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="V886" s="4" t="s">
         <v>203</v>
@@ -78940,11 +78940,11 @@
       </c>
       <c r="N887" s="4"/>
       <c r="O887" s="4" t="s">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="P887" s="5"/>
       <c r="Q887" s="4" t="s">
-        <v>3356</v>
+        <v>3357</v>
       </c>
       <c r="R887" s="4" t="s">
         <v>56</v>
@@ -78965,7 +78965,7 @@
       </c>
       <c r="Y887" s="4"/>
       <c r="Z887" s="4" t="s">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="AA887" s="4" t="s">
         <v>252</v>
@@ -79016,11 +79016,11 @@
         <v>92</v>
       </c>
       <c r="O888" s="4" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="P888" s="5"/>
       <c r="Q888" s="4" t="s">
-        <v>3359</v>
+        <v>3360</v>
       </c>
       <c r="R888" s="4" t="s">
         <v>63</v>
@@ -79041,7 +79041,7 @@
       </c>
       <c r="Y888" s="4"/>
       <c r="Z888" s="4" t="s">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="AA888" s="4" t="s">
         <v>65</v>
@@ -79090,11 +79090,11 @@
       </c>
       <c r="N889" s="4"/>
       <c r="O889" s="4" t="s">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="P889" s="5"/>
       <c r="Q889" s="4" t="s">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="R889" s="4" t="s">
         <v>56</v>
@@ -79115,7 +79115,7 @@
       </c>
       <c r="Y889" s="4"/>
       <c r="Z889" s="4" t="s">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="AA889" s="4" t="s">
         <v>48</v>
@@ -79157,7 +79157,7 @@
       </c>
       <c r="K890" s="4"/>
       <c r="L890" s="4" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="M890" s="4" t="s">
         <v>943</v>
@@ -79166,11 +79166,11 @@
         <v>56</v>
       </c>
       <c r="O890" s="4" t="s">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="P890" s="5"/>
       <c r="Q890" s="4" t="s">
-        <v>3365</v>
+        <v>3366</v>
       </c>
       <c r="R890" s="4" t="s">
         <v>56</v>
@@ -79191,7 +79191,7 @@
       </c>
       <c r="Y890" s="4"/>
       <c r="Z890" s="4" t="s">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="AA890" s="4" t="s">
         <v>48</v>
@@ -79229,24 +79229,24 @@
         <v>1690</v>
       </c>
       <c r="J891" s="4" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="K891" s="4"/>
       <c r="L891" s="4" t="s">
         <v>253</v>
       </c>
       <c r="M891" s="4" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="N891" s="4">
         <v>29</v>
       </c>
       <c r="O891" s="4" t="s">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="P891" s="5"/>
       <c r="Q891" s="4" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="R891" s="4" t="s">
         <v>63</v>
@@ -79258,7 +79258,7 @@
         <v>0</v>
       </c>
       <c r="U891" s="4" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="V891" s="4" t="s">
         <v>75</v>
@@ -79271,7 +79271,7 @@
       </c>
       <c r="Y891" s="4"/>
       <c r="Z891" s="4" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="AA891" s="4" t="s">
         <v>65</v>
@@ -79309,24 +79309,24 @@
         <v>1690</v>
       </c>
       <c r="J892" s="4" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="K892" s="4"/>
       <c r="L892" s="4" t="s">
         <v>459</v>
       </c>
       <c r="M892" s="4" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="N892" s="4">
         <v>42</v>
       </c>
       <c r="O892" s="4" t="s">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="P892" s="5"/>
       <c r="Q892" s="4" t="s">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="R892" s="4" t="s">
         <v>63</v>
@@ -79385,18 +79385,18 @@
         <v>1864</v>
       </c>
       <c r="J893" s="4" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="K893" s="4"/>
       <c r="L893" s="4"/>
       <c r="M893" s="4"/>
       <c r="N893" s="4"/>
       <c r="O893" s="4" t="s">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="P893" s="5"/>
       <c r="Q893" s="4" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="R893" s="4" t="s">
         <v>63</v>
@@ -79417,7 +79417,7 @@
       </c>
       <c r="Y893" s="4"/>
       <c r="Z893" s="4" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="AA893" s="4"/>
       <c r="AB893" s="4" t="s">
@@ -79453,18 +79453,18 @@
         <v>1864</v>
       </c>
       <c r="J894" s="4" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="K894" s="4"/>
       <c r="L894" s="4"/>
       <c r="M894" s="4"/>
       <c r="N894" s="4"/>
       <c r="O894" s="4" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="P894" s="5"/>
       <c r="Q894" s="4" t="s">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="R894" s="4" t="s">
         <v>63</v>
@@ -79485,7 +79485,7 @@
       </c>
       <c r="Y894" s="4"/>
       <c r="Z894" s="4" t="s">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="AA894" s="4"/>
       <c r="AB894" s="4" t="s">
@@ -79518,21 +79518,21 @@
         <v>1690</v>
       </c>
       <c r="I895" s="4" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="J895" s="4" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="K895" s="4"/>
       <c r="L895" s="4"/>
       <c r="M895" s="4"/>
       <c r="N895" s="4"/>
       <c r="O895" s="4" t="s">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="P895" s="5"/>
       <c r="Q895" s="4" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="R895" s="4" t="s">
         <v>56</v>
@@ -79544,7 +79544,7 @@
         <v>0</v>
       </c>
       <c r="U895" s="4" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="V895" s="4" t="s">
         <v>317</v>
@@ -79557,7 +79557,7 @@
       </c>
       <c r="Y895" s="4"/>
       <c r="Z895" s="4" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="AA895" s="4" t="s">
         <v>65</v>
@@ -79595,24 +79595,24 @@
         <v>1690</v>
       </c>
       <c r="J896" s="4" t="s">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="K896" s="4"/>
       <c r="L896" s="4" t="s">
         <v>2450</v>
       </c>
       <c r="M896" s="4" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="N896" s="4">
         <v>5</v>
       </c>
       <c r="O896" s="4" t="s">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="P896" s="5"/>
       <c r="Q896" s="4" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="R896" s="4" t="s">
         <v>43</v>
@@ -79633,7 +79633,7 @@
       </c>
       <c r="Y896" s="4"/>
       <c r="Z896" s="4" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="AA896" s="4" t="s">
         <v>252</v>
@@ -79671,24 +79671,24 @@
         <v>1690</v>
       </c>
       <c r="J897" s="4" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="K897" s="4"/>
       <c r="L897" s="4" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="M897" s="4" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="N897" s="4">
         <v>26</v>
       </c>
       <c r="O897" s="4" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="P897" s="5"/>
       <c r="Q897" s="4" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="R897" s="4" t="s">
         <v>63</v>
@@ -79700,7 +79700,7 @@
         <v>7</v>
       </c>
       <c r="U897" s="4" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="V897" s="4" t="s">
         <v>125</v>
@@ -79713,7 +79713,7 @@
       </c>
       <c r="Y897" s="4"/>
       <c r="Z897" s="4" t="s">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="AA897" s="4" t="s">
         <v>77</v>
@@ -79751,24 +79751,24 @@
         <v>1690</v>
       </c>
       <c r="J898" s="4" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="K898" s="4"/>
       <c r="L898" s="4" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="M898" s="4" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="N898" s="4">
         <v>16</v>
       </c>
       <c r="O898" s="4" t="s">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="P898" s="5"/>
       <c r="Q898" s="4" t="s">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="R898" s="4" t="s">
         <v>63</v>
@@ -79789,7 +79789,7 @@
       </c>
       <c r="Y898" s="4"/>
       <c r="Z898" s="4" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="AA898" s="4"/>
       <c r="AB898" s="4" t="s">
@@ -79825,18 +79825,18 @@
         <v>1690</v>
       </c>
       <c r="J899" s="4" t="s">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="K899" s="4"/>
       <c r="L899" s="4"/>
       <c r="M899" s="4"/>
       <c r="N899" s="4"/>
       <c r="O899" s="4" t="s">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="P899" s="5"/>
       <c r="Q899" s="4" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="R899" s="4" t="s">
         <v>56</v>
@@ -79857,7 +79857,7 @@
       </c>
       <c r="Y899" s="4"/>
       <c r="Z899" s="4" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="AA899" s="4"/>
       <c r="AB899" s="4" t="s">
@@ -79893,18 +79893,18 @@
         <v>1690</v>
       </c>
       <c r="J900" s="4" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="K900" s="4"/>
       <c r="L900" s="4"/>
       <c r="M900" s="4"/>
       <c r="N900" s="4"/>
       <c r="O900" s="4" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="P900" s="5"/>
       <c r="Q900" s="4" t="s">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="R900" s="4" t="s">
         <v>296</v>
@@ -79963,7 +79963,7 @@
         <v>1690</v>
       </c>
       <c r="J901" s="4" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="K901" s="4"/>
       <c r="L901" s="4" t="s">
@@ -79974,11 +79974,11 @@
         <v>143</v>
       </c>
       <c r="O901" s="4" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="P901" s="5"/>
       <c r="Q901" s="4" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="R901" s="4" t="s">
         <v>296</v>
@@ -79999,7 +79999,7 @@
       </c>
       <c r="Y901" s="4"/>
       <c r="Z901" s="4" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="AA901" s="4" t="s">
         <v>48</v>
@@ -80037,7 +80037,7 @@
         <v>1690</v>
       </c>
       <c r="J902" s="4" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="K902" s="4"/>
       <c r="L902" s="4" t="s">
@@ -80048,11 +80048,11 @@
         <v>161</v>
       </c>
       <c r="O902" s="4" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="P902" s="5"/>
       <c r="Q902" s="4" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="R902" s="4" t="s">
         <v>296</v>
@@ -80073,7 +80073,7 @@
       </c>
       <c r="Y902" s="4"/>
       <c r="Z902" s="4" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="AA902" s="4" t="s">
         <v>48</v>
@@ -80111,7 +80111,7 @@
         <v>1690</v>
       </c>
       <c r="J903" s="4" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="K903" s="4"/>
       <c r="L903" s="4" t="s">
@@ -80122,11 +80122,11 @@
         <v>174</v>
       </c>
       <c r="O903" s="4" t="s">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="P903" s="5"/>
       <c r="Q903" s="4" t="s">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="R903" s="4" t="s">
         <v>296</v>
@@ -80138,10 +80138,10 @@
         <v>0</v>
       </c>
       <c r="U903" s="4" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="V903" s="4" t="s">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="W903" s="4">
         <v>9</v>
@@ -80151,7 +80151,7 @@
       </c>
       <c r="Y903" s="4"/>
       <c r="Z903" s="4" t="s">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="AA903" s="4" t="s">
         <v>65</v>
@@ -80193,20 +80193,20 @@
       </c>
       <c r="K904" s="4"/>
       <c r="L904" s="4" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="M904" s="4" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="N904" s="4">
         <v>24</v>
       </c>
       <c r="O904" s="4" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="P904" s="5"/>
       <c r="Q904" s="4" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="R904" s="4" t="s">
         <v>63</v>
@@ -80218,7 +80218,7 @@
         <v>0</v>
       </c>
       <c r="U904" s="4" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="V904" s="4" t="s">
         <v>363</v>
@@ -80231,7 +80231,7 @@
       </c>
       <c r="Y904" s="4"/>
       <c r="Z904" s="4" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="AA904" s="4"/>
       <c r="AB904" s="4" t="s">
@@ -80271,20 +80271,20 @@
       </c>
       <c r="K905" s="4"/>
       <c r="L905" s="4" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="M905" s="4" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="N905" s="4">
         <v>54</v>
       </c>
       <c r="O905" s="4" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="P905" s="5"/>
       <c r="Q905" s="4" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="R905" s="4" t="s">
         <v>63</v>
@@ -80305,7 +80305,7 @@
       </c>
       <c r="Y905" s="4"/>
       <c r="Z905" s="4" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="AA905" s="4" t="s">
         <v>48</v>
@@ -80343,7 +80343,7 @@
         <v>1690</v>
       </c>
       <c r="J906" s="4" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="K906" s="4"/>
       <c r="L906" s="4" t="s">
@@ -80356,11 +80356,11 @@
         <v>2</v>
       </c>
       <c r="O906" s="4" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="P906" s="5"/>
       <c r="Q906" s="4" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="R906" s="4" t="s">
         <v>43</v>
@@ -80381,7 +80381,7 @@
       </c>
       <c r="Y906" s="4"/>
       <c r="Z906" s="4" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="AA906" s="4"/>
       <c r="AB906" s="4" t="s">
@@ -80417,7 +80417,7 @@
         <v>1690</v>
       </c>
       <c r="J907" s="4" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="K907" s="4"/>
       <c r="L907" s="4" t="s">
@@ -80430,11 +80430,11 @@
         <v>10</v>
       </c>
       <c r="O907" s="4" t="s">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="P907" s="5"/>
       <c r="Q907" s="4" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="R907" s="4" t="s">
         <v>63</v>
@@ -80455,7 +80455,7 @@
       </c>
       <c r="Y907" s="4"/>
       <c r="Z907" s="4" t="s">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="AA907" s="4"/>
       <c r="AB907" s="4" t="s">
@@ -80491,7 +80491,7 @@
         <v>1690</v>
       </c>
       <c r="J908" s="4" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="K908" s="4"/>
       <c r="L908" s="4" t="s">
@@ -80504,11 +80504,11 @@
         <v>46</v>
       </c>
       <c r="O908" s="4" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="P908" s="5"/>
       <c r="Q908" s="4" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="R908" s="4" t="s">
         <v>56</v>
@@ -80529,7 +80529,7 @@
       </c>
       <c r="Y908" s="4"/>
       <c r="Z908" s="4" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="AA908" s="4" t="s">
         <v>48</v>
@@ -80567,24 +80567,24 @@
         <v>1690</v>
       </c>
       <c r="J909" s="4" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="K909" s="4"/>
       <c r="L909" s="4" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="M909" s="4" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="N909" s="4">
         <v>21</v>
       </c>
       <c r="O909" s="4" t="s">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="P909" s="5"/>
       <c r="Q909" s="4" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="R909" s="4" t="s">
         <v>63</v>
@@ -80596,7 +80596,7 @@
         <v>4</v>
       </c>
       <c r="U909" s="4" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="V909" s="4" t="s">
         <v>363</v>
@@ -80609,7 +80609,7 @@
       </c>
       <c r="Y909" s="4"/>
       <c r="Z909" s="4" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="AA909" s="4" t="s">
         <v>48</v>
@@ -80647,7 +80647,7 @@
         <v>1690</v>
       </c>
       <c r="J910" s="4" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="K910" s="4"/>
       <c r="L910" s="4" t="s">
@@ -80660,11 +80660,11 @@
         <v>11</v>
       </c>
       <c r="O910" s="4" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="P910" s="5"/>
       <c r="Q910" s="4" t="s">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="R910" s="4" t="s">
         <v>63</v>
@@ -80676,7 +80676,7 @@
         <v>0</v>
       </c>
       <c r="U910" s="4" t="s">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="V910" s="4" t="s">
         <v>102</v>
@@ -80689,7 +80689,7 @@
       </c>
       <c r="Y910" s="4"/>
       <c r="Z910" s="4" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="AA910" s="4" t="s">
         <v>48</v>
@@ -80727,11 +80727,11 @@
         <v>1690</v>
       </c>
       <c r="J911" s="4" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="K911" s="4"/>
       <c r="L911" s="4" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="M911" s="4" t="s">
         <v>657</v>
@@ -80740,11 +80740,11 @@
         <v>20</v>
       </c>
       <c r="O911" s="4" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="P911" s="5"/>
       <c r="Q911" s="4" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="R911" s="4" t="s">
         <v>63</v>
@@ -80756,7 +80756,7 @@
         <v>0</v>
       </c>
       <c r="U911" s="4" t="s">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="V911" s="4" t="s">
         <v>125</v>
@@ -80769,7 +80769,7 @@
       </c>
       <c r="Y911" s="4"/>
       <c r="Z911" s="4" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="AA911" s="4"/>
       <c r="AB911" s="4" t="s">
@@ -80812,7 +80812,7 @@
       <c r="M912" s="4"/>
       <c r="N912" s="4"/>
       <c r="O912" s="4" t="s">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="P912" s="5"/>
       <c r="Q912" s="4" t="s">
@@ -80828,7 +80828,7 @@
         <v>4</v>
       </c>
       <c r="U912" s="4" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="V912" s="4" t="s">
         <v>198</v>
@@ -80841,7 +80841,7 @@
       </c>
       <c r="Y912" s="4"/>
       <c r="Z912" s="4" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="AA912" s="4"/>
       <c r="AB912" s="4" t="s">
@@ -80884,11 +80884,11 @@
       <c r="M913" s="4"/>
       <c r="N913" s="4"/>
       <c r="O913" s="4" t="s">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="P913" s="5"/>
       <c r="Q913" s="4" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="R913" s="4" t="s">
         <v>63</v>
@@ -80900,7 +80900,7 @@
         <v>0</v>
       </c>
       <c r="U913" s="4" t="s">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="V913" s="4" t="s">
         <v>1552</v>
@@ -80913,7 +80913,7 @@
       </c>
       <c r="Y913" s="4"/>
       <c r="Z913" s="4" t="s">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="AA913" s="4" t="s">
         <v>48</v>
@@ -80964,11 +80964,11 @@
         <v>951</v>
       </c>
       <c r="O914" s="4" t="s">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="P914" s="5"/>
       <c r="Q914" s="4" t="s">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="R914" s="4" t="s">
         <v>56</v>
@@ -80989,7 +80989,7 @@
       </c>
       <c r="Y914" s="4"/>
       <c r="Z914" s="4" t="s">
-        <v>3468</v>
+        <v>3469</v>
       </c>
       <c r="AA914" s="4"/>
       <c r="AB914" s="4" t="s">
@@ -81025,11 +81025,11 @@
         <v>1690</v>
       </c>
       <c r="J915" s="4" t="s">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="K915" s="4"/>
       <c r="L915" s="4" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="M915" s="4" t="s">
         <v>2406</v>
@@ -81038,11 +81038,11 @@
         <v>39</v>
       </c>
       <c r="O915" s="4" t="s">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="P915" s="5"/>
       <c r="Q915" s="4" t="s">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="R915" s="4" t="s">
         <v>63</v>
@@ -81054,7 +81054,7 @@
         <v>0</v>
       </c>
       <c r="U915" s="4" t="s">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="V915" s="4" t="s">
         <v>363</v>
@@ -81067,7 +81067,7 @@
       </c>
       <c r="Y915" s="4"/>
       <c r="Z915" s="4" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="AA915" s="4" t="s">
         <v>48</v>
@@ -81105,11 +81105,11 @@
         <v>1690</v>
       </c>
       <c r="J916" s="4" t="s">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="K916" s="4"/>
       <c r="L916" s="4" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="M916" s="4" t="s">
         <v>2406</v>
@@ -81118,11 +81118,11 @@
         <v>49</v>
       </c>
       <c r="O916" s="4" t="s">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="P916" s="5"/>
       <c r="Q916" s="4" t="s">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="R916" s="4" t="s">
         <v>63</v>
@@ -81143,7 +81143,7 @@
       </c>
       <c r="Y916" s="4"/>
       <c r="Z916" s="4" t="s">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="AA916" s="4" t="s">
         <v>48</v>
@@ -81163,7 +81163,7 @@
         <v>162444259</v>
       </c>
       <c r="D917" s="4" t="s">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="E917" s="4">
         <v>5666850</v>
@@ -81181,11 +81181,11 @@
         <v>1690</v>
       </c>
       <c r="J917" s="4" t="s">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="K917" s="4"/>
       <c r="L917" s="4" t="s">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="M917" s="4" t="s">
         <v>1594</v>
@@ -81194,11 +81194,11 @@
         <v>49</v>
       </c>
       <c r="O917" s="4" t="s">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="P917" s="5"/>
       <c r="Q917" s="4" t="s">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="R917" s="4" t="s">
         <v>43</v>
@@ -81219,7 +81219,7 @@
       </c>
       <c r="Y917" s="4"/>
       <c r="Z917" s="4" t="s">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="AA917" s="4" t="s">
         <v>65</v>
@@ -81257,24 +81257,24 @@
         <v>1690</v>
       </c>
       <c r="J918" s="4" t="s">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="K918" s="4"/>
       <c r="L918" s="4" t="s">
         <v>2075</v>
       </c>
       <c r="M918" s="4" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="N918" s="4">
         <v>5</v>
       </c>
       <c r="O918" s="4" t="s">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="P918" s="5"/>
       <c r="Q918" s="4" t="s">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="R918" s="4" t="s">
         <v>56</v>
@@ -81295,7 +81295,7 @@
       </c>
       <c r="Y918" s="4"/>
       <c r="Z918" s="4" t="s">
-        <v>3487</v>
+        <v>3488</v>
       </c>
       <c r="AA918" s="4" t="s">
         <v>65</v>
@@ -81327,13 +81327,13 @@
         <v>36</v>
       </c>
       <c r="H919" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I919" s="4" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="J919" s="4" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="K919" s="4"/>
       <c r="L919" s="4" t="s">
@@ -81346,11 +81346,11 @@
         <v>1</v>
       </c>
       <c r="O919" s="4" t="s">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="P919" s="5"/>
       <c r="Q919" s="4" t="s">
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="R919" s="4" t="s">
         <v>43</v>
@@ -81371,7 +81371,7 @@
       </c>
       <c r="Y919" s="4"/>
       <c r="Z919" s="4" t="s">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="AA919" s="4" t="s">
         <v>488</v>
@@ -81403,13 +81403,13 @@
         <v>36</v>
       </c>
       <c r="H920" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I920" s="4" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="J920" s="4" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="K920" s="4"/>
       <c r="L920" s="4" t="s">
@@ -81422,11 +81422,11 @@
         <v>100</v>
       </c>
       <c r="O920" s="4" t="s">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="P920" s="5"/>
       <c r="Q920" s="4" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="R920" s="4" t="s">
         <v>56</v>
@@ -81438,7 +81438,7 @@
         <v>0</v>
       </c>
       <c r="U920" s="4" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
       <c r="V920" s="4" t="s">
         <v>363</v>
@@ -81451,7 +81451,7 @@
       </c>
       <c r="Y920" s="4"/>
       <c r="Z920" s="4" t="s">
-        <v>3496</v>
+        <v>3497</v>
       </c>
       <c r="AA920" s="4"/>
       <c r="AB920" s="4" t="s">
@@ -81481,24 +81481,24 @@
         <v>36</v>
       </c>
       <c r="H921" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I921" s="4" t="s">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="J921" s="4" t="s">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="K921" s="4"/>
       <c r="L921" s="4"/>
       <c r="M921" s="4"/>
       <c r="N921" s="4"/>
       <c r="O921" s="4" t="s">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="P921" s="5"/>
       <c r="Q921" s="4" t="s">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="R921" s="4" t="s">
         <v>63</v>
@@ -81510,10 +81510,10 @@
         <v>1</v>
       </c>
       <c r="U921" s="4" t="s">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="V921" s="4" t="s">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="W921" s="4">
         <v>30</v>
@@ -81523,7 +81523,7 @@
       </c>
       <c r="Y921" s="4"/>
       <c r="Z921" s="4" t="s">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="AA921" s="4" t="s">
         <v>48</v>
@@ -81555,24 +81555,24 @@
         <v>36</v>
       </c>
       <c r="H922" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I922" s="4" t="s">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="J922" s="4" t="s">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="K922" s="4"/>
       <c r="L922" s="4"/>
       <c r="M922" s="4"/>
       <c r="N922" s="4"/>
       <c r="O922" s="4" t="s">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="P922" s="5"/>
       <c r="Q922" s="4" t="s">
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="R922" s="4" t="s">
         <v>278</v>
@@ -81584,7 +81584,7 @@
         <v>70</v>
       </c>
       <c r="U922" s="4" t="s">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="V922" s="4" t="s">
         <v>614</v>
@@ -81629,17 +81629,17 @@
         <v>36</v>
       </c>
       <c r="H923" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I923" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J923" s="4" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="K923" s="4"/>
       <c r="L923" s="4" t="s">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="M923" s="4" t="s">
         <v>253</v>
@@ -81648,11 +81648,11 @@
         <v>6</v>
       </c>
       <c r="O923" s="4" t="s">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="P923" s="5"/>
       <c r="Q923" s="4" t="s">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="R923" s="4" t="s">
         <v>43</v>
@@ -81673,7 +81673,7 @@
       </c>
       <c r="Y923" s="4"/>
       <c r="Z923" s="4" t="s">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="AA923" s="4" t="s">
         <v>48</v>
@@ -81687,7 +81687,7 @@
         <v>1000</v>
       </c>
       <c r="B924" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C924" s="4">
         <v>160297305</v>
@@ -81705,17 +81705,17 @@
         <v>36</v>
       </c>
       <c r="H924" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I924" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J924" s="4" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="K924" s="4"/>
       <c r="L924" s="4" t="s">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="M924" s="4" t="s">
         <v>247</v>
@@ -81724,11 +81724,11 @@
         <v>15</v>
       </c>
       <c r="O924" s="4" t="s">
-        <v>3515</v>
+        <v>3516</v>
       </c>
       <c r="P924" s="5"/>
       <c r="Q924" s="4" t="s">
-        <v>3516</v>
+        <v>3517</v>
       </c>
       <c r="R924" s="4" t="s">
         <v>56</v>
@@ -81740,7 +81740,7 @@
         <v>2</v>
       </c>
       <c r="U924" s="4" t="s">
-        <v>3517</v>
+        <v>3518</v>
       </c>
       <c r="V924" s="4" t="s">
         <v>125</v>
@@ -81749,7 +81749,7 @@
         <v>37</v>
       </c>
       <c r="X924" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y924" s="4"/>
       <c r="Z924" s="4" t="s">
@@ -81785,13 +81785,13 @@
         <v>36</v>
       </c>
       <c r="H925" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I925" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J925" s="4" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="K925" s="4"/>
       <c r="L925" s="4" t="s">
@@ -81845,7 +81845,7 @@
         <v>1000</v>
       </c>
       <c r="B926" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C926" s="4">
         <v>162928062</v>
@@ -81863,13 +81863,13 @@
         <v>36</v>
       </c>
       <c r="H926" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I926" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J926" s="4" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="K926" s="4"/>
       <c r="L926" s="4" t="s">
@@ -81905,7 +81905,7 @@
         <v>2</v>
       </c>
       <c r="X926" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y926" s="4"/>
       <c r="Z926" s="4" t="s">
@@ -81923,7 +81923,7 @@
         <v>1000</v>
       </c>
       <c r="B927" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C927" s="4">
         <v>162940318</v>
@@ -81941,10 +81941,10 @@
         <v>36</v>
       </c>
       <c r="H927" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I927" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J927" s="4" t="s">
         <v>69</v>
@@ -81985,7 +81985,7 @@
         <v>2</v>
       </c>
       <c r="X927" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y927" s="4"/>
       <c r="Z927" s="4" t="s">
@@ -82021,10 +82021,10 @@
         <v>36</v>
       </c>
       <c r="H928" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I928" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J928" s="4" t="s">
         <v>84</v>
@@ -82099,10 +82099,10 @@
         <v>36</v>
       </c>
       <c r="H929" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I929" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J929" s="4" t="s">
         <v>84</v>
@@ -82173,10 +82173,10 @@
         <v>36</v>
       </c>
       <c r="H930" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I930" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J930" s="4" t="s">
         <v>84</v>
@@ -82253,10 +82253,10 @@
         <v>36</v>
       </c>
       <c r="H931" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I931" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J931" s="4" t="s">
         <v>84</v>
@@ -82327,10 +82327,10 @@
         <v>36</v>
       </c>
       <c r="H932" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I932" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J932" s="4" t="s">
         <v>84</v>
@@ -82401,10 +82401,10 @@
         <v>36</v>
       </c>
       <c r="H933" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I933" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J933" s="4" t="s">
         <v>84</v>
@@ -82437,7 +82437,7 @@
         <v>3547</v>
       </c>
       <c r="V933" s="4" t="s">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="W933" s="4">
         <v>62</v>
@@ -82461,7 +82461,7 @@
         <v>1000</v>
       </c>
       <c r="B934" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C934" s="4">
         <v>162919408</v>
@@ -82479,10 +82479,10 @@
         <v>36</v>
       </c>
       <c r="H934" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I934" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J934" s="4" t="s">
         <v>84</v>
@@ -82521,7 +82521,7 @@
         <v>2</v>
       </c>
       <c r="X934" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y934" s="4"/>
       <c r="Z934" s="4" t="s">
@@ -82557,10 +82557,10 @@
         <v>36</v>
       </c>
       <c r="H935" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I935" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J935" s="4" t="s">
         <v>84</v>
@@ -82633,10 +82633,10 @@
         <v>36</v>
       </c>
       <c r="H936" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I936" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J936" s="4" t="s">
         <v>84</v>
@@ -82707,10 +82707,10 @@
         <v>36</v>
       </c>
       <c r="H937" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I937" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J937" s="4" t="s">
         <v>84</v>
@@ -82787,10 +82787,10 @@
         <v>36</v>
       </c>
       <c r="H938" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I938" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J938" s="4" t="s">
         <v>84</v>
@@ -82861,10 +82861,10 @@
         <v>36</v>
       </c>
       <c r="H939" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I939" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J939" s="4" t="s">
         <v>84</v>
@@ -82939,10 +82939,10 @@
         <v>36</v>
       </c>
       <c r="H940" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I940" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J940" s="4" t="s">
         <v>84</v>
@@ -83013,10 +83013,10 @@
         <v>36</v>
       </c>
       <c r="H941" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I941" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J941" s="4" t="s">
         <v>84</v>
@@ -83087,10 +83087,10 @@
         <v>36</v>
       </c>
       <c r="H942" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I942" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J942" s="4" t="s">
         <v>84</v>
@@ -83165,10 +83165,10 @@
         <v>36</v>
       </c>
       <c r="H943" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I943" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J943" s="4" t="s">
         <v>84</v>
@@ -83245,10 +83245,10 @@
         <v>36</v>
       </c>
       <c r="H944" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I944" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J944" s="4" t="s">
         <v>84</v>
@@ -83319,7 +83319,7 @@
         <v>36</v>
       </c>
       <c r="H945" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I945" s="4" t="s">
         <v>3585</v>
@@ -83379,7 +83379,7 @@
         <v>1000</v>
       </c>
       <c r="B946" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C946" s="4">
         <v>162940991</v>
@@ -83397,10 +83397,10 @@
         <v>36</v>
       </c>
       <c r="H946" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I946" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J946" s="4" t="s">
         <v>3589</v>
@@ -83439,7 +83439,7 @@
         <v>2</v>
       </c>
       <c r="X946" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y946" s="4"/>
       <c r="Z946" s="4" t="s">
@@ -83475,7 +83475,7 @@
         <v>36</v>
       </c>
       <c r="H947" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I947" s="4" t="s">
         <v>3594</v>
@@ -83555,10 +83555,10 @@
         <v>36</v>
       </c>
       <c r="H948" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I948" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J948" s="4" t="s">
         <v>2448</v>
@@ -83633,7 +83633,7 @@
         <v>36</v>
       </c>
       <c r="H949" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I949" s="4" t="s">
         <v>3605</v>
@@ -83707,7 +83707,7 @@
         <v>36</v>
       </c>
       <c r="H950" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I950" s="4" t="s">
         <v>3610</v>
@@ -83777,10 +83777,10 @@
         <v>36</v>
       </c>
       <c r="H951" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I951" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J951" s="4" t="s">
         <v>3614</v>
@@ -83853,10 +83853,10 @@
         <v>36</v>
       </c>
       <c r="H952" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I952" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J952" s="4" t="s">
         <v>3614</v>
@@ -83915,7 +83915,7 @@
         <v>1000</v>
       </c>
       <c r="B953" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C953" s="4">
         <v>162912341</v>
@@ -83933,10 +83933,10 @@
         <v>36</v>
       </c>
       <c r="H953" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I953" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J953" s="4" t="s">
         <v>3623</v>
@@ -83973,7 +83973,7 @@
         <v>2</v>
       </c>
       <c r="X953" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y953" s="4"/>
       <c r="Z953" s="4" t="s">
@@ -84009,10 +84009,10 @@
         <v>36</v>
       </c>
       <c r="H954" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I954" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J954" s="4" t="s">
         <v>1137</v>
@@ -84089,10 +84089,10 @@
         <v>36</v>
       </c>
       <c r="H955" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I955" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J955" s="4" t="s">
         <v>1137</v>
@@ -84163,7 +84163,7 @@
         <v>36</v>
       </c>
       <c r="H956" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I956" s="4" t="s">
         <v>3636</v>
@@ -84235,10 +84235,10 @@
         <v>36</v>
       </c>
       <c r="H957" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I957" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J957" s="4" t="s">
         <v>3641</v>
@@ -84297,7 +84297,7 @@
         <v>1000</v>
       </c>
       <c r="B958" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C958" s="4">
         <v>159956953</v>
@@ -84315,10 +84315,10 @@
         <v>36</v>
       </c>
       <c r="H958" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I958" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J958" s="4" t="s">
         <v>3646</v>
@@ -84355,7 +84355,7 @@
         <v>41</v>
       </c>
       <c r="X958" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y958" s="4"/>
       <c r="Z958" s="4" t="s">
@@ -84371,7 +84371,7 @@
         <v>1000</v>
       </c>
       <c r="B959" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C959" s="4">
         <v>161708047</v>
@@ -84389,10 +84389,10 @@
         <v>36</v>
       </c>
       <c r="H959" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I959" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J959" s="4" t="s">
         <v>3646</v>
@@ -84429,7 +84429,7 @@
         <v>16</v>
       </c>
       <c r="X959" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y959" s="4"/>
       <c r="Z959" s="4" t="s">
@@ -84463,10 +84463,10 @@
         <v>36</v>
       </c>
       <c r="H960" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I960" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J960" s="4" t="s">
         <v>3653</v>
@@ -84525,7 +84525,7 @@
         <v>1000</v>
       </c>
       <c r="B961" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C961" s="4">
         <v>162900395</v>
@@ -84543,10 +84543,10 @@
         <v>36</v>
       </c>
       <c r="H961" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I961" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J961" s="4" t="s">
         <v>3653</v>
@@ -84583,7 +84583,7 @@
         <v>2</v>
       </c>
       <c r="X961" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y961" s="4"/>
       <c r="Z961" s="4" t="s">
@@ -84601,7 +84601,7 @@
         <v>1000</v>
       </c>
       <c r="B962" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C962" s="4">
         <v>160567997</v>
@@ -84619,10 +84619,10 @@
         <v>36</v>
       </c>
       <c r="H962" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I962" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J962" s="4" t="s">
         <v>1284</v>
@@ -84663,7 +84663,7 @@
         <v>34</v>
       </c>
       <c r="X962" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y962" s="4"/>
       <c r="Z962" s="4" t="s">
@@ -84699,10 +84699,10 @@
         <v>36</v>
       </c>
       <c r="H963" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I963" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J963" s="4" t="s">
         <v>3667</v>
@@ -84749,7 +84749,7 @@
         <v>1000</v>
       </c>
       <c r="B964" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C964" s="4">
         <v>159638091</v>
@@ -84767,10 +84767,10 @@
         <v>36</v>
       </c>
       <c r="H964" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I964" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J964" s="4" t="s">
         <v>3667</v>
@@ -84807,7 +84807,7 @@
         <v>44</v>
       </c>
       <c r="X964" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y964" s="4"/>
       <c r="Z964" s="4" t="s">
@@ -84825,7 +84825,7 @@
         <v>1000</v>
       </c>
       <c r="B965" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C965" s="4">
         <v>162986498</v>
@@ -84843,10 +84843,10 @@
         <v>36</v>
       </c>
       <c r="H965" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I965" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J965" s="4" t="s">
         <v>3674</v>
@@ -84883,7 +84883,7 @@
         <v>1</v>
       </c>
       <c r="X965" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y965" s="4"/>
       <c r="Z965" s="4" t="s">
@@ -84919,10 +84919,10 @@
         <v>36</v>
       </c>
       <c r="H966" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I966" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J966" s="4" t="s">
         <v>979</v>
@@ -84993,10 +84993,10 @@
         <v>36</v>
       </c>
       <c r="H967" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I967" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J967" s="4" t="s">
         <v>979</v>
@@ -85049,7 +85049,7 @@
         <v>1000</v>
       </c>
       <c r="B968" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C968" s="4">
         <v>162936616</v>
@@ -85067,10 +85067,10 @@
         <v>36</v>
       </c>
       <c r="H968" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I968" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="J968" s="4" t="s">
         <v>979</v>
@@ -85105,7 +85105,7 @@
         <v>2</v>
       </c>
       <c r="X968" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y968" s="4"/>
       <c r="Z968" s="4" t="s">
@@ -85141,7 +85141,7 @@
         <v>36</v>
       </c>
       <c r="H969" s="4" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="I969" s="4" t="s">
         <v>3688</v>
@@ -86128,7 +86128,7 @@
         <v>560</v>
       </c>
       <c r="M982" s="4" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="N982" s="4">
         <v>7</v>
@@ -86589,7 +86589,7 @@
       </c>
       <c r="K988" s="4"/>
       <c r="L988" s="4" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="M988" s="4" t="s">
         <v>705</v>
@@ -86665,7 +86665,7 @@
       </c>
       <c r="K989" s="4"/>
       <c r="L989" s="4" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="M989" s="4" t="s">
         <v>560</v>
@@ -88801,7 +88801,7 @@
         <v>1000</v>
       </c>
       <c r="B1018" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C1018" s="4">
         <v>135317231</v>
@@ -88853,7 +88853,7 @@
         <v>365</v>
       </c>
       <c r="X1018" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y1018" s="4"/>
       <c r="Z1018" s="4" t="s">
@@ -88869,13 +88869,13 @@
         <v>1000</v>
       </c>
       <c r="B1019" s="4" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C1019" s="4">
         <v>161590131</v>
       </c>
       <c r="D1019" s="4" t="s">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="E1019" s="4">
         <v>7606222</v>
@@ -88925,7 +88925,7 @@
         <v>17</v>
       </c>
       <c r="X1019" s="4" t="s">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="Y1019" s="4"/>
       <c r="Z1019" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 16:31:00</t>
+    <t>09/08/2026 a las 17:31:23</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 17:31:23</t>
+    <t>09/08/2026 a las 18:30:58</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 19:30:58</t>
+    <t>09/08/2026 a las 20:30:54</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 20:30:54</t>
+    <t>09/08/2026 a las 21:30:47</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 21:30:47</t>
+    <t>09/08/2026 a las 22:30:51</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 22:30:51</t>
+    <t>09/08/2026 a las 23:30:51</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>19/08/2026 a las 07:28:03</t>
+    <t>19/08/2026 a las 07:31:11</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>30/08/2026 a las 19:24:29</t>
+    <t>30/08/2026 a las 19:31:08</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>30/08/2026 a las 19:31:08</t>
+    <t>30/08/2026 a las 20:31:06</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>30/08/2026 a las 20:31:06</t>
+    <t>30/08/2026 a las 21:30:56</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3659">
   <si>
     <t>DELTEC - GUAJIRA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>05/09/2026 a las 13:56:28</t>
+    <t>05/09/2026 a las 14:04:29</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -10929,21 +10929,6 @@
   </si>
   <si>
     <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Agraciano MOntano Quintero cc.16468415 cel. 3135720117 manifiesta que el predio esta desocupado tomar lectura verificar estado de desocupacion y conexiones llamar predio solo</t>
-  </si>
-  <si>
-    <t>CL 18 CR 2 - 32 DPL EH4371</t>
-  </si>
-  <si>
-    <t>LINDARTE  LUIS</t>
-  </si>
-  <si>
-    <t>001366212-MC988</t>
-  </si>
-  <si>
-    <t>Comprometida</t>
-  </si>
-  <si>
-    <t>Investigar Dano medidor yo acometida Reportar incidencia en viviendA OSF nic 5601572tel 3234661516Claudia LopezSolo en su predio es</t>
   </si>
   <si>
     <t>CR 13 # CL 5 - 20 DPL EH5414</t>
@@ -11400,7 +11385,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB929"/>
+  <dimension ref="A1:AB928"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -81221,13 +81206,13 @@
         <v>600</v>
       </c>
       <c r="C923" s="4">
-        <v>165796146</v>
+        <v>165797438</v>
       </c>
       <c r="D923" s="4" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="E923" s="4">
-        <v>5601572</v>
+        <v>7907151</v>
       </c>
       <c r="F923" s="4" t="s">
         <v>318</v>
@@ -81242,18 +81227,16 @@
         <v>3624</v>
       </c>
       <c r="J923" s="4" t="s">
-        <v>3634</v>
+        <v>758</v>
       </c>
       <c r="K923" s="4"/>
       <c r="L923" s="4" t="s">
-        <v>330</v>
+        <v>683</v>
       </c>
       <c r="M923" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="N923" s="4">
-        <v>32</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N923" s="4"/>
       <c r="O923" s="4" t="s">
         <v>3638</v>
       </c>
@@ -81262,7 +81245,7 @@
         <v>3639</v>
       </c>
       <c r="R923" s="4" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="S923" s="4">
         <v>0</v>
@@ -81270,23 +81253,21 @@
       <c r="T923" s="4">
         <v>0</v>
       </c>
-      <c r="U923" s="4" t="s">
-        <v>3640</v>
-      </c>
-      <c r="V923" s="4" t="s">
-        <v>253</v>
-      </c>
+      <c r="U923" s="4"/>
+      <c r="V923" s="4"/>
       <c r="W923" s="4">
         <v>1</v>
       </c>
       <c r="X923" s="4" t="s">
-        <v>3641</v>
+        <v>347</v>
       </c>
       <c r="Y923" s="4"/>
       <c r="Z923" s="4" t="s">
-        <v>3642</v>
-      </c>
-      <c r="AA923" s="4"/>
+        <v>3640</v>
+      </c>
+      <c r="AA923" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AB923" s="4" t="s">
         <v>47</v>
       </c>
@@ -81299,13 +81280,13 @@
         <v>600</v>
       </c>
       <c r="C924" s="4">
-        <v>165797438</v>
+        <v>165797363</v>
       </c>
       <c r="D924" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E924" s="4">
-        <v>7907151</v>
+        <v>5613476</v>
       </c>
       <c r="F924" s="4" t="s">
         <v>318</v>
@@ -81324,27 +81305,27 @@
       </c>
       <c r="K924" s="4"/>
       <c r="L924" s="4" t="s">
-        <v>683</v>
+        <v>550</v>
       </c>
       <c r="M924" s="4" t="s">
-        <v>288</v>
+        <v>851</v>
       </c>
       <c r="N924" s="4"/>
       <c r="O924" s="4" t="s">
-        <v>3643</v>
+        <v>3641</v>
       </c>
       <c r="P924" s="5"/>
       <c r="Q924" s="4" t="s">
-        <v>3644</v>
+        <v>3642</v>
       </c>
       <c r="R924" s="4" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="S924" s="4">
-        <v>0</v>
+        <v>4957093.1</v>
       </c>
       <c r="T924" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U924" s="4"/>
       <c r="V924" s="4"/>
@@ -81356,10 +81337,10 @@
       </c>
       <c r="Y924" s="4"/>
       <c r="Z924" s="4" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="AA924" s="4" t="s">
-        <v>46</v>
+        <v>279</v>
       </c>
       <c r="AB924" s="4" t="s">
         <v>47</v>
@@ -81370,16 +81351,16 @@
         <v>1000</v>
       </c>
       <c r="B925" s="4" t="s">
-        <v>600</v>
+        <v>33</v>
       </c>
       <c r="C925" s="4">
-        <v>165797363</v>
+        <v>165516713</v>
       </c>
       <c r="D925" s="4" t="s">
-        <v>48</v>
+        <v>317</v>
       </c>
       <c r="E925" s="4">
-        <v>5613476</v>
+        <v>8384812</v>
       </c>
       <c r="F925" s="4" t="s">
         <v>318</v>
@@ -81394,47 +81375,47 @@
         <v>3624</v>
       </c>
       <c r="J925" s="4" t="s">
-        <v>758</v>
+        <v>1361</v>
       </c>
       <c r="K925" s="4"/>
       <c r="L925" s="4" t="s">
-        <v>550</v>
+        <v>86</v>
       </c>
       <c r="M925" s="4" t="s">
-        <v>851</v>
-      </c>
-      <c r="N925" s="4"/>
+        <v>388</v>
+      </c>
+      <c r="N925" s="4">
+        <v>108</v>
+      </c>
       <c r="O925" s="4" t="s">
-        <v>3646</v>
+        <v>3644</v>
       </c>
       <c r="P925" s="5"/>
       <c r="Q925" s="4" t="s">
-        <v>3647</v>
+        <v>3645</v>
       </c>
       <c r="R925" s="4" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="S925" s="4">
-        <v>4957093.1</v>
+        <v>0</v>
       </c>
       <c r="T925" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U925" s="4"/>
       <c r="V925" s="4"/>
       <c r="W925" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X925" s="4" t="s">
-        <v>347</v>
+        <v>44</v>
       </c>
       <c r="Y925" s="4"/>
       <c r="Z925" s="4" t="s">
-        <v>3648</v>
-      </c>
-      <c r="AA925" s="4" t="s">
-        <v>279</v>
-      </c>
+        <v>3646</v>
+      </c>
+      <c r="AA925" s="4"/>
       <c r="AB925" s="4" t="s">
         <v>47</v>
       </c>
@@ -81447,13 +81428,13 @@
         <v>33</v>
       </c>
       <c r="C926" s="4">
-        <v>165516713</v>
+        <v>135317231</v>
       </c>
       <c r="D926" s="4" t="s">
-        <v>317</v>
+        <v>634</v>
       </c>
       <c r="E926" s="4">
-        <v>8384812</v>
+        <v>8310140</v>
       </c>
       <c r="F926" s="4" t="s">
         <v>318</v>
@@ -81465,27 +81446,21 @@
         <v>3623</v>
       </c>
       <c r="I926" s="4" t="s">
-        <v>3624</v>
+        <v>3647</v>
       </c>
       <c r="J926" s="4" t="s">
-        <v>1361</v>
+        <v>3647</v>
       </c>
       <c r="K926" s="4"/>
-      <c r="L926" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="M926" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="N926" s="4">
-        <v>108</v>
-      </c>
+      <c r="L926" s="4"/>
+      <c r="M926" s="4"/>
+      <c r="N926" s="4"/>
       <c r="O926" s="4" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="P926" s="5"/>
       <c r="Q926" s="4" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="R926" s="4" t="s">
         <v>136</v>
@@ -81499,18 +81474,18 @@
       <c r="U926" s="4"/>
       <c r="V926" s="4"/>
       <c r="W926" s="4">
-        <v>3</v>
+        <v>402</v>
       </c>
       <c r="X926" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y926" s="4"/>
       <c r="Z926" s="4" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="AA926" s="4"/>
       <c r="AB926" s="4" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="927" spans="1:28">
@@ -81521,13 +81496,13 @@
         <v>33</v>
       </c>
       <c r="C927" s="4">
-        <v>135317231</v>
+        <v>163954467</v>
       </c>
       <c r="D927" s="4" t="s">
-        <v>634</v>
+        <v>209</v>
       </c>
       <c r="E927" s="4">
-        <v>8310140</v>
+        <v>7604842</v>
       </c>
       <c r="F927" s="4" t="s">
         <v>318</v>
@@ -81539,46 +81514,54 @@
         <v>3623</v>
       </c>
       <c r="I927" s="4" t="s">
+        <v>3624</v>
+      </c>
+      <c r="J927" s="4" t="s">
+        <v>3651</v>
+      </c>
+      <c r="K927" s="4"/>
+      <c r="L927" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="M927" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="N927" s="4">
+        <v>112</v>
+      </c>
+      <c r="O927" s="4" t="s">
         <v>3652</v>
-      </c>
-      <c r="J927" s="4" t="s">
-        <v>3652</v>
-      </c>
-      <c r="K927" s="4"/>
-      <c r="L927" s="4"/>
-      <c r="M927" s="4"/>
-      <c r="N927" s="4"/>
-      <c r="O927" s="4" t="s">
-        <v>3653</v>
       </c>
       <c r="P927" s="5"/>
       <c r="Q927" s="4" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="R927" s="4" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="S927" s="4">
-        <v>0</v>
+        <v>29325266.23</v>
       </c>
       <c r="T927" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U927" s="4"/>
       <c r="V927" s="4"/>
       <c r="W927" s="4">
-        <v>402</v>
+        <v>24</v>
       </c>
       <c r="X927" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y927" s="4"/>
       <c r="Z927" s="4" t="s">
-        <v>3655</v>
-      </c>
-      <c r="AA927" s="4"/>
+        <v>3654</v>
+      </c>
+      <c r="AA927" s="4" t="s">
+        <v>238</v>
+      </c>
       <c r="AB927" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="928" spans="1:28">
@@ -81589,13 +81572,13 @@
         <v>33</v>
       </c>
       <c r="C928" s="4">
-        <v>163954467</v>
+        <v>165291268</v>
       </c>
       <c r="D928" s="4" t="s">
-        <v>209</v>
+        <v>97</v>
       </c>
       <c r="E928" s="4">
-        <v>7604842</v>
+        <v>5614893</v>
       </c>
       <c r="F928" s="4" t="s">
         <v>318</v>
@@ -81610,130 +81593,54 @@
         <v>3624</v>
       </c>
       <c r="J928" s="4" t="s">
-        <v>3656</v>
+        <v>3651</v>
       </c>
       <c r="K928" s="4"/>
       <c r="L928" s="4" t="s">
-        <v>644</v>
+        <v>169</v>
       </c>
       <c r="M928" s="4" t="s">
         <v>584</v>
       </c>
       <c r="N928" s="4">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="O928" s="4" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="P928" s="5"/>
       <c r="Q928" s="4" t="s">
-        <v>3658</v>
+        <v>3656</v>
       </c>
       <c r="R928" s="4" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="S928" s="4">
-        <v>29325266.23</v>
+        <v>29249.67</v>
       </c>
       <c r="T928" s="4">
-        <v>4</v>
-      </c>
-      <c r="U928" s="4"/>
-      <c r="V928" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U928" s="4" t="s">
+        <v>3657</v>
+      </c>
+      <c r="V928" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="W928" s="4">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="X928" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y928" s="4"/>
       <c r="Z928" s="4" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="AA928" s="4" t="s">
-        <v>238</v>
+        <v>85</v>
       </c>
       <c r="AB928" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="929" spans="1:28">
-      <c r="A929" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B929" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C929" s="4">
-        <v>165291268</v>
-      </c>
-      <c r="D929" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E929" s="4">
-        <v>5614893</v>
-      </c>
-      <c r="F929" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="G929" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H929" s="4" t="s">
-        <v>3623</v>
-      </c>
-      <c r="I929" s="4" t="s">
-        <v>3624</v>
-      </c>
-      <c r="J929" s="4" t="s">
-        <v>3656</v>
-      </c>
-      <c r="K929" s="4"/>
-      <c r="L929" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="M929" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="N929" s="4">
-        <v>4</v>
-      </c>
-      <c r="O929" s="4" t="s">
-        <v>3660</v>
-      </c>
-      <c r="P929" s="5"/>
-      <c r="Q929" s="4" t="s">
-        <v>3661</v>
-      </c>
-      <c r="R929" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="S929" s="4">
-        <v>29249.67</v>
-      </c>
-      <c r="T929" s="4">
-        <v>1</v>
-      </c>
-      <c r="U929" s="4" t="s">
-        <v>3662</v>
-      </c>
-      <c r="V929" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="W929" s="4">
-        <v>8</v>
-      </c>
-      <c r="X929" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y929" s="4"/>
-      <c r="Z929" s="4" t="s">
-        <v>3663</v>
-      </c>
-      <c r="AA929" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB929" s="4" t="s">
         <v>47</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>11/09/2026 a las 07:22:35</t>
+    <t>11/09/2026 a las 07:31:38</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -39747,7 +39747,7 @@
         <v>15</v>
       </c>
       <c r="X371" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y371" s="4"/>
       <c r="Z371" s="4" t="s">
@@ -40449,7 +40449,7 @@
         <v>15</v>
       </c>
       <c r="X380" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y380" s="4"/>
       <c r="Z380" s="4" t="s">
@@ -43939,7 +43939,7 @@
         <v>15</v>
       </c>
       <c r="X425" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y425" s="4"/>
       <c r="Z425" s="4" t="s">
@@ -44019,7 +44019,7 @@
         <v>10</v>
       </c>
       <c r="X426" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y426" s="4"/>
       <c r="Z426" s="4" t="s">
@@ -44095,7 +44095,7 @@
         <v>15</v>
       </c>
       <c r="X427" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y427" s="4"/>
       <c r="Z427" s="4" t="s">
@@ -44865,7 +44865,7 @@
         <v>15</v>
       </c>
       <c r="X437" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y437" s="4"/>
       <c r="Z437" s="4" t="s">
@@ -45093,7 +45093,7 @@
         <v>15</v>
       </c>
       <c r="X440" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y440" s="4"/>
       <c r="Z440" s="4" t="s">
@@ -51191,7 +51191,7 @@
         <v>15</v>
       </c>
       <c r="X520" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y520" s="4"/>
       <c r="Z520" s="4" t="s">
@@ -56923,7 +56923,7 @@
         <v>2</v>
       </c>
       <c r="X594" s="4" t="s">
-        <v>937</v>
+        <v>308</v>
       </c>
       <c r="Y594" s="4"/>
       <c r="Z594" s="4" t="s">
